--- a/JIBAR_FRA_SWAPS.xlsx
+++ b/JIBAR_FRA_SWAPS.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pv01-my.sharepoint.com/personal/gordon_pv01_co_za/Documents/Dev Repos/ZARONIA_SARB/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pv01-my.sharepoint.com/personal/gordon_pv01_co_za/Documents/Projects/zaronia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B814A78-7EB1-4270-BC93-EA09DFB8DBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{1B814A78-7EB1-4270-BC93-EA09DFB8DBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19F14F68-F54A-4BAF-B533-D096B88B7841}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{34753434-5FEB-48FC-8487-529A3B1ADE64}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{34753434-5FEB-48FC-8487-529A3B1ADE64}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -79,7 +79,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,8 +107,19 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -121,8 +132,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2AA84"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -158,12 +180,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -177,6 +214,13 @@
     <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -512,13 +556,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ACB4107-8137-49C4-AFE3-6FF31C87A0A4}">
-  <dimension ref="A1:K548"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K631"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -553,7 +597,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>45231</v>
       </c>
@@ -588,7 +632,7 @@
         <v>9.7100000000000009</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>45232</v>
       </c>
@@ -623,7 +667,7 @@
         <v>9.61</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>45233</v>
       </c>
@@ -658,7 +702,7 @@
         <v>9.51</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>45236</v>
       </c>
@@ -693,7 +737,7 @@
         <v>9.58</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>45237</v>
       </c>
@@ -728,7 +772,7 @@
         <v>9.57</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>45238</v>
       </c>
@@ -763,7 +807,7 @@
         <v>9.57</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>45239</v>
       </c>
@@ -798,7 +842,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>45240</v>
       </c>
@@ -833,7 +877,7 @@
         <v>9.52</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>45243</v>
       </c>
@@ -868,7 +912,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>45244</v>
       </c>
@@ -903,7 +947,7 @@
         <v>9.35</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>45245</v>
       </c>
@@ -938,7 +982,7 @@
         <v>9.34</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>45246</v>
       </c>
@@ -973,7 +1017,7 @@
         <v>9.2100000000000009</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>45247</v>
       </c>
@@ -1008,7 +1052,7 @@
         <v>9.23</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>45250</v>
       </c>
@@ -1043,7 +1087,7 @@
         <v>9.2200000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>45251</v>
       </c>
@@ -1078,7 +1122,7 @@
         <v>9.18</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>45252</v>
       </c>
@@ -1113,7 +1157,7 @@
         <v>9.35</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>45253</v>
       </c>
@@ -1148,7 +1192,7 @@
         <v>9.34</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>45254</v>
       </c>
@@ -1183,7 +1227,7 @@
         <v>9.42</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>45257</v>
       </c>
@@ -1218,7 +1262,7 @@
         <v>9.34</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>45258</v>
       </c>
@@ -1253,7 +1297,7 @@
         <v>9.2100000000000009</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>45259</v>
       </c>
@@ -1288,7 +1332,7 @@
         <v>9.15</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>45260</v>
       </c>
@@ -1323,7 +1367,7 @@
         <v>9.2200000000000006</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>45261</v>
       </c>
@@ -1358,7 +1402,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>45264</v>
       </c>
@@ -1393,7 +1437,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>45265</v>
       </c>
@@ -1428,7 +1472,7 @@
         <v>9.27</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>45266</v>
       </c>
@@ -1463,7 +1507,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>45267</v>
       </c>
@@ -1498,7 +1542,7 @@
         <v>9.17</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>45268</v>
       </c>
@@ -1533,7 +1577,7 @@
         <v>9.23</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>45271</v>
       </c>
@@ -1568,7 +1612,7 @@
         <v>9.2899999999999991</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>45272</v>
       </c>
@@ -1603,7 +1647,7 @@
         <v>9.24</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>45273</v>
       </c>
@@ -1638,7 +1682,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>45274</v>
       </c>
@@ -1673,7 +1717,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>45275</v>
       </c>
@@ -1708,7 +1752,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>45278</v>
       </c>
@@ -1743,7 +1787,7 @@
         <v>9.0150000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>45279</v>
       </c>
@@ -1778,7 +1822,7 @@
         <v>8.9600000000000009</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>45280</v>
       </c>
@@ -1813,7 +1857,7 @@
         <v>8.9600000000000009</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>45281</v>
       </c>
@@ -1848,7 +1892,7 @@
         <v>8.9791666666666679</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>45282</v>
       </c>
@@ -1883,7 +1927,7 @@
         <v>8.9983333333333348</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>45285</v>
       </c>
@@ -1918,7 +1962,7 @@
         <v>9.0175000000000018</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>45286</v>
       </c>
@@ -1953,7 +1997,7 @@
         <v>9.0366666666666688</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>45287</v>
       </c>
@@ -1988,7 +2032,7 @@
         <v>9.0558333333333358</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>45288</v>
       </c>
@@ -2023,7 +2067,7 @@
         <v>9.0750000000000028</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>45289</v>
       </c>
@@ -2058,7 +2102,7 @@
         <v>9.0941666666666698</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>45292</v>
       </c>
@@ -2093,7 +2137,7 @@
         <v>9.1133333333333368</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>45293</v>
       </c>
@@ -2128,7 +2172,7 @@
         <v>9.1325000000000038</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>45294</v>
       </c>
@@ -2163,7 +2207,7 @@
         <v>9.1516666666666708</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>45295</v>
       </c>
@@ -2198,7 +2242,7 @@
         <v>9.1708333333333378</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>45296</v>
       </c>
@@ -2233,7 +2277,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>45299</v>
       </c>
@@ -2268,7 +2312,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>45300</v>
       </c>
@@ -2303,7 +2347,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>45301</v>
       </c>
@@ -2338,7 +2382,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>45302</v>
       </c>
@@ -2373,7 +2417,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>45303</v>
       </c>
@@ -2408,7 +2452,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>45306</v>
       </c>
@@ -2443,7 +2487,7 @@
         <v>9.1300000000000008</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>45307</v>
       </c>
@@ -2478,7 +2522,7 @@
         <v>9.18</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>45308</v>
       </c>
@@ -2513,7 +2557,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>45309</v>
       </c>
@@ -2548,7 +2592,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>45310</v>
       </c>
@@ -2583,7 +2627,7 @@
         <v>9.2100000000000009</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>45313</v>
       </c>
@@ -2618,7 +2662,7 @@
         <v>9.18</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>45314</v>
       </c>
@@ -2653,7 +2697,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>45315</v>
       </c>
@@ -2688,7 +2732,7 @@
         <v>9.2100000000000009</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>45316</v>
       </c>
@@ -2723,7 +2767,7 @@
         <v>9.17</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>45317</v>
       </c>
@@ -2758,7 +2802,7 @@
         <v>9.2100000000000009</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>45320</v>
       </c>
@@ -2793,7 +2837,7 @@
         <v>9.2100000000000009</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>45321</v>
       </c>
@@ -2828,7 +2872,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>45322</v>
       </c>
@@ -2863,7 +2907,7 @@
         <v>9.17</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>45323</v>
       </c>
@@ -2898,7 +2942,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>45324</v>
       </c>
@@ -2933,7 +2977,7 @@
         <v>9.15</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>45327</v>
       </c>
@@ -2968,7 +3012,7 @@
         <v>9.2799999999999994</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>45328</v>
       </c>
@@ -3003,7 +3047,7 @@
         <v>9.2200000000000006</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>45329</v>
       </c>
@@ -3038,7 +3082,7 @@
         <v>9.2200000000000006</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>45330</v>
       </c>
@@ -3073,7 +3117,7 @@
         <v>9.31</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>45331</v>
       </c>
@@ -3108,7 +3152,7 @@
         <v>9.33</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>45334</v>
       </c>
@@ -3143,7 +3187,7 @@
         <v>9.41</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>45335</v>
       </c>
@@ -3178,7 +3222,7 @@
         <v>9.41</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>45336</v>
       </c>
@@ -3213,7 +3257,7 @@
         <v>9.39</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>45337</v>
       </c>
@@ -3248,7 +3292,7 @@
         <v>9.35</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>45338</v>
       </c>
@@ -3283,7 +3327,7 @@
         <v>9.4050000000000011</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>45341</v>
       </c>
@@ -3318,7 +3362,7 @@
         <v>9.4600000000000009</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>45342</v>
       </c>
@@ -3353,7 +3397,7 @@
         <v>9.3800000000000008</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>45343</v>
       </c>
@@ -3388,7 +3432,7 @@
         <v>9.35</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>45344</v>
       </c>
@@ -3423,7 +3467,7 @@
         <v>9.39</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>45345</v>
       </c>
@@ -3458,7 +3502,7 @@
         <v>9.5399999999999991</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>45348</v>
       </c>
@@ -3493,7 +3537,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>45349</v>
       </c>
@@ -3528,7 +3572,7 @@
         <v>9.5299999999999994</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>45350</v>
       </c>
@@ -3563,7 +3607,7 @@
         <v>9.56</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>45351</v>
       </c>
@@ -3598,7 +3642,7 @@
         <v>9.5299999999999994</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>45352</v>
       </c>
@@ -3633,7 +3677,7 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>45355</v>
       </c>
@@ -3668,7 +3712,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>45356</v>
       </c>
@@ -3703,7 +3747,7 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>45357</v>
       </c>
@@ -3738,7 +3782,7 @@
         <v>9.44</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>45358</v>
       </c>
@@ -3773,7 +3817,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>45359</v>
       </c>
@@ -3808,7 +3852,7 @@
         <v>9.3699999999999992</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>45362</v>
       </c>
@@ -3843,7 +3887,7 @@
         <v>9.379999999999999</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>45363</v>
       </c>
@@ -3878,7 +3922,7 @@
         <v>9.39</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>45364</v>
       </c>
@@ -3913,7 +3957,7 @@
         <v>9.39</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>45365</v>
       </c>
@@ -3948,7 +3992,7 @@
         <v>9.5299999999999994</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>45366</v>
       </c>
@@ -3983,7 +4027,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>45369</v>
       </c>
@@ -4018,7 +4062,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>45370</v>
       </c>
@@ -4053,7 +4097,7 @@
         <v>9.6300000000000008</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>45371</v>
       </c>
@@ -4088,7 +4132,7 @@
         <v>9.6300000000000008</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>45372</v>
       </c>
@@ -4123,7 +4167,7 @@
         <v>9.6300000000000008</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>45373</v>
       </c>
@@ -4158,7 +4202,7 @@
         <v>9.6300000000000008</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>45376</v>
       </c>
@@ -4193,7 +4237,7 @@
         <v>9.66</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>45377</v>
       </c>
@@ -4228,7 +4272,7 @@
         <v>9.7799999999999994</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>45378</v>
       </c>
@@ -4263,7 +4307,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>45379</v>
       </c>
@@ -4298,7 +4342,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>45380</v>
       </c>
@@ -4333,7 +4377,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>45383</v>
       </c>
@@ -4368,7 +4412,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>45384</v>
       </c>
@@ -4403,7 +4447,7 @@
         <v>9.84</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>45385</v>
       </c>
@@ -4438,7 +4482,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>45386</v>
       </c>
@@ -4473,7 +4517,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>45387</v>
       </c>
@@ -4508,7 +4552,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>45390</v>
       </c>
@@ -4543,7 +4587,7 @@
         <v>9.84</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>45391</v>
       </c>
@@ -4578,7 +4622,7 @@
         <v>9.7799999999999994</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>45392</v>
       </c>
@@ -4613,7 +4657,7 @@
         <v>9.91</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>45393</v>
       </c>
@@ -4648,7 +4692,7 @@
         <v>9.98</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>45394</v>
       </c>
@@ -4683,7 +4727,7 @@
         <v>10.050000000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>45397</v>
       </c>
@@ -4718,7 +4762,7 @@
         <v>10.15</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>45398</v>
       </c>
@@ -4753,7 +4797,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>45399</v>
       </c>
@@ -4788,7 +4832,7 @@
         <v>10.14</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>45400</v>
       </c>
@@ -4823,7 +4867,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>45401</v>
       </c>
@@ -4858,7 +4902,7 @@
         <v>10.17</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>45404</v>
       </c>
@@ -4893,7 +4937,7 @@
         <v>10.16</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>45405</v>
       </c>
@@ -4928,7 +4972,7 @@
         <v>10.08</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>45406</v>
       </c>
@@ -4963,7 +5007,7 @@
         <v>10.17</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>45407</v>
       </c>
@@ -4998,7 +5042,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>45408</v>
       </c>
@@ -5033,7 +5077,7 @@
         <v>10.11</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>45411</v>
       </c>
@@ -5068,7 +5112,7 @@
         <v>10.01</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>45412</v>
       </c>
@@ -5103,7 +5147,7 @@
         <v>9.99</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>45413</v>
       </c>
@@ -5138,7 +5182,7 @@
         <v>9.99</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>45414</v>
       </c>
@@ -5173,7 +5217,7 @@
         <v>9.9450000000000003</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>45415</v>
       </c>
@@ -5208,7 +5252,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>45418</v>
       </c>
@@ -5243,7 +5287,7 @@
         <v>9.85</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>45419</v>
       </c>
@@ -5278,7 +5322,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>45420</v>
       </c>
@@ -5313,7 +5357,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>45421</v>
       </c>
@@ -5348,7 +5392,7 @@
         <v>9.83</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>45422</v>
       </c>
@@ -5383,7 +5427,7 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>45425</v>
       </c>
@@ -5418,7 +5462,7 @@
         <v>9.7799999999999994</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>45426</v>
       </c>
@@ -5453,7 +5497,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>45427</v>
       </c>
@@ -5488,7 +5532,7 @@
         <v>9.67</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>45428</v>
       </c>
@@ -5523,7 +5567,7 @@
         <v>9.6300000000000008</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>45429</v>
       </c>
@@ -5558,7 +5602,7 @@
         <v>9.64</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>45432</v>
       </c>
@@ -5593,7 +5637,7 @@
         <v>9.6300000000000008</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>45433</v>
       </c>
@@ -5628,7 +5672,7 @@
         <v>9.57</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>45434</v>
       </c>
@@ -5663,7 +5707,7 @@
         <v>9.58</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>45435</v>
       </c>
@@ -5698,7 +5742,7 @@
         <v>9.69</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>45436</v>
       </c>
@@ -5733,7 +5777,7 @@
         <v>9.7799999999999994</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>45439</v>
       </c>
@@ -5768,7 +5812,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>45440</v>
       </c>
@@ -5803,7 +5847,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>45441</v>
       </c>
@@ -5838,7 +5882,7 @@
         <v>9.7200000000000006</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>45442</v>
       </c>
@@ -5873,7 +5917,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>45443</v>
       </c>
@@ -5908,7 +5952,7 @@
         <v>9.89</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>45446</v>
       </c>
@@ -5943,7 +5987,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>45447</v>
       </c>
@@ -5978,7 +6022,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>45448</v>
       </c>
@@ -6013,7 +6057,7 @@
         <v>9.8699999999999992</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>45449</v>
       </c>
@@ -6048,7 +6092,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>45450</v>
       </c>
@@ -6083,7 +6127,7 @@
         <v>9.67</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>45453</v>
       </c>
@@ -6118,7 +6162,7 @@
         <v>9.58</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>45454</v>
       </c>
@@ -6153,7 +6197,7 @@
         <v>9.52</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>45455</v>
       </c>
@@ -6188,7 +6232,7 @@
         <v>9.43</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>45456</v>
       </c>
@@ -6223,7 +6267,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>45457</v>
       </c>
@@ -6258,7 +6302,7 @@
         <v>9.42</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>45460</v>
       </c>
@@ -6293,7 +6337,7 @@
         <v>9.42</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>45461</v>
       </c>
@@ -6328,7 +6372,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>45462</v>
       </c>
@@ -6363,7 +6407,7 @@
         <v>9.11</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>45463</v>
       </c>
@@ -6398,7 +6442,7 @@
         <v>9.16</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>45464</v>
       </c>
@@ -6433,7 +6477,7 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>45467</v>
       </c>
@@ -6468,7 +6512,7 @@
         <v>9.18</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>45468</v>
       </c>
@@ -6503,7 +6547,7 @@
         <v>9.14</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>45469</v>
       </c>
@@ -6538,7 +6582,7 @@
         <v>9.16</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>45470</v>
       </c>
@@ -6573,7 +6617,7 @@
         <v>9.31</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>45471</v>
       </c>
@@ -6608,7 +6652,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>45474</v>
       </c>
@@ -6643,7 +6687,7 @@
         <v>9.24</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>45475</v>
       </c>
@@ -6678,7 +6722,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>45476</v>
       </c>
@@ -6713,7 +6757,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>45477</v>
       </c>
@@ -6748,7 +6792,7 @@
         <v>9.17</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>45478</v>
       </c>
@@ -6783,7 +6827,7 @@
         <v>9.14</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>45481</v>
       </c>
@@ -6818,7 +6862,7 @@
         <v>9.1166666666666671</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>45482</v>
       </c>
@@ -6853,7 +6897,7 @@
         <v>9.0933333333333337</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>45483</v>
       </c>
@@ -6888,7 +6932,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>45484</v>
       </c>
@@ -6923,7 +6967,7 @@
         <v>8.9699999999999989</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>45485</v>
       </c>
@@ -6958,7 +7002,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>45488</v>
       </c>
@@ -6993,7 +7037,7 @@
         <v>8.94</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>45489</v>
       </c>
@@ -7028,7 +7072,7 @@
         <v>8.9450000000000003</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>45490</v>
       </c>
@@ -7063,7 +7107,7 @@
         <v>8.9499999999999993</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>45491</v>
       </c>
@@ -7098,7 +7142,7 @@
         <v>8.9700000000000006</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>45492</v>
       </c>
@@ -7133,7 +7177,7 @@
         <v>8.9333333333333336</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>45495</v>
       </c>
@@ -7168,7 +7212,7 @@
         <v>8.8966666666666665</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>45496</v>
       </c>
@@ -7203,7 +7247,7 @@
         <v>8.86</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>45497</v>
       </c>
@@ -7238,7 +7282,7 @@
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>45498</v>
       </c>
@@ -7273,7 +7317,7 @@
         <v>8.91</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>45499</v>
       </c>
@@ -7308,7 +7352,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>45502</v>
       </c>
@@ -7343,7 +7387,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>45503</v>
       </c>
@@ -7378,7 +7422,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>45504</v>
       </c>
@@ -7413,7 +7457,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>45505</v>
       </c>
@@ -7448,7 +7492,7 @@
         <v>8.65</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>45506</v>
       </c>
@@ -7483,7 +7527,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>45509</v>
       </c>
@@ -7518,7 +7562,7 @@
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>45510</v>
       </c>
@@ -7553,7 +7597,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>45511</v>
       </c>
@@ -7588,7 +7632,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>45512</v>
       </c>
@@ -7623,7 +7667,7 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>45513</v>
       </c>
@@ -7658,7 +7702,7 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>45516</v>
       </c>
@@ -7693,7 +7737,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>45517</v>
       </c>
@@ -7728,7 +7772,7 @@
         <v>8.64</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>45518</v>
       </c>
@@ -7763,7 +7807,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>45519</v>
       </c>
@@ -7798,7 +7842,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>45520</v>
       </c>
@@ -7833,7 +7877,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>45523</v>
       </c>
@@ -7868,7 +7912,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>45524</v>
       </c>
@@ -7903,7 +7947,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>45525</v>
       </c>
@@ -7938,7 +7982,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>45526</v>
       </c>
@@ -7973,7 +8017,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>45527</v>
       </c>
@@ -8008,7 +8052,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>45530</v>
       </c>
@@ -8043,7 +8087,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>45531</v>
       </c>
@@ -8078,7 +8122,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>45532</v>
       </c>
@@ -8113,7 +8157,7 @@
         <v>8.67</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>45533</v>
       </c>
@@ -8148,7 +8192,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>45534</v>
       </c>
@@ -8183,7 +8227,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>45537</v>
       </c>
@@ -8218,7 +8262,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>45538</v>
       </c>
@@ -8253,7 +8297,7 @@
         <v>8.68</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>45539</v>
       </c>
@@ -8288,7 +8332,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>45540</v>
       </c>
@@ -8323,7 +8367,7 @@
         <v>8.5299999999999994</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>45541</v>
       </c>
@@ -8358,7 +8402,7 @@
         <v>8.52</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>45544</v>
       </c>
@@ -8393,7 +8437,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>45545</v>
       </c>
@@ -8428,7 +8472,7 @@
         <v>8.52</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>45546</v>
       </c>
@@ -8463,7 +8507,7 @@
         <v>8.48</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>45547</v>
       </c>
@@ -8498,7 +8542,7 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>45548</v>
       </c>
@@ -8533,7 +8577,7 @@
         <v>8.4600000000000009</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>45551</v>
       </c>
@@ -8568,7 +8612,7 @@
         <v>8.3800000000000008</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>45552</v>
       </c>
@@ -8603,7 +8647,7 @@
         <v>8.3800000000000008</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>45553</v>
       </c>
@@ -8638,7 +8682,7 @@
         <v>8.4700000000000006</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>45554</v>
       </c>
@@ -8673,7 +8717,7 @@
         <v>8.4600000000000009</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>45555</v>
       </c>
@@ -8708,7 +8752,7 @@
         <v>8.48</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>45558</v>
       </c>
@@ -8743,7 +8787,7 @@
         <v>8.48</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>45559</v>
       </c>
@@ -8778,7 +8822,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>45560</v>
       </c>
@@ -8813,7 +8857,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>45561</v>
       </c>
@@ -8848,7 +8892,7 @@
         <v>8.43</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>45562</v>
       </c>
@@ -8883,7 +8927,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>45565</v>
       </c>
@@ -8918,7 +8962,7 @@
         <v>8.43</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>45566</v>
       </c>
@@ -8953,7 +8997,7 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>45567</v>
       </c>
@@ -8988,7 +9032,7 @@
         <v>8.58</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>45568</v>
       </c>
@@ -9023,7 +9067,7 @@
         <v>8.6300000000000008</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>45569</v>
       </c>
@@ -9058,7 +9102,7 @@
         <v>8.67</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>45572</v>
       </c>
@@ -9093,7 +9137,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>45573</v>
       </c>
@@ -9128,7 +9172,7 @@
         <v>8.74</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>45574</v>
       </c>
@@ -9163,7 +9207,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>45575</v>
       </c>
@@ -9198,7 +9242,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>45576</v>
       </c>
@@ -9233,7 +9277,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>45579</v>
       </c>
@@ -9268,7 +9312,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>45580</v>
       </c>
@@ -9303,7 +9347,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>45581</v>
       </c>
@@ -9338,7 +9382,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>45582</v>
       </c>
@@ -9373,7 +9417,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>45583</v>
       </c>
@@ -9408,7 +9452,7 @@
         <v>8.86</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>45586</v>
       </c>
@@ -9443,7 +9487,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>45587</v>
       </c>
@@ -9478,7 +9522,7 @@
         <v>8.9699999999999989</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>45588</v>
       </c>
@@ -9513,7 +9557,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>45589</v>
       </c>
@@ -9548,7 +9592,7 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>45590</v>
       </c>
@@ -9583,7 +9627,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>45593</v>
       </c>
@@ -9618,7 +9662,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>45594</v>
       </c>
@@ -9653,7 +9697,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>45595</v>
       </c>
@@ -9688,7 +9732,7 @@
         <v>8.91</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>45596</v>
       </c>
@@ -9723,7 +9767,7 @@
         <v>8.94</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>45597</v>
       </c>
@@ -9758,7 +9802,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>45600</v>
       </c>
@@ -9793,7 +9837,7 @@
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>45601</v>
       </c>
@@ -9828,7 +9872,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>45602</v>
       </c>
@@ -9863,7 +9907,7 @@
         <v>8.98</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>45603</v>
       </c>
@@ -9898,7 +9942,7 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>45604</v>
       </c>
@@ -9933,7 +9977,7 @@
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>45607</v>
       </c>
@@ -9968,7 +10012,7 @@
         <v>8.86</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>45608</v>
       </c>
@@ -10003,7 +10047,7 @@
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>45609</v>
       </c>
@@ -10038,7 +10082,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>45610</v>
       </c>
@@ -10073,7 +10117,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>45611</v>
       </c>
@@ -10108,7 +10152,7 @@
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>45614</v>
       </c>
@@ -10143,7 +10187,7 @@
         <v>8.74</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>45615</v>
       </c>
@@ -10178,7 +10222,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>45616</v>
       </c>
@@ -10213,7 +10257,7 @@
         <v>8.66</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>45617</v>
       </c>
@@ -10248,7 +10292,7 @@
         <v>8.58</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>45618</v>
       </c>
@@ -10283,7 +10327,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>45621</v>
       </c>
@@ -10318,7 +10362,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>45622</v>
       </c>
@@ -10353,7 +10397,7 @@
         <v>8.65</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>45623</v>
       </c>
@@ -10388,7 +10432,7 @@
         <v>8.6199999999999992</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>45624</v>
       </c>
@@ -10423,7 +10467,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>45625</v>
       </c>
@@ -10458,7 +10502,7 @@
         <v>8.48</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>45628</v>
       </c>
@@ -10493,7 +10537,7 @@
         <v>8.4700000000000006</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>45629</v>
       </c>
@@ -10528,7 +10572,7 @@
         <v>8.4600000000000009</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>45630</v>
       </c>
@@ -10563,7 +10607,7 @@
         <v>8.52</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>45631</v>
       </c>
@@ -10598,7 +10642,7 @@
         <v>8.52</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>45632</v>
       </c>
@@ -10633,7 +10677,7 @@
         <v>8.58</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>45635</v>
       </c>
@@ -10668,7 +10712,7 @@
         <v>8.52</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>45636</v>
       </c>
@@ -10703,7 +10747,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>45637</v>
       </c>
@@ -10738,7 +10782,7 @@
         <v>8.49</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>45638</v>
       </c>
@@ -10773,7 +10817,7 @@
         <v>8.4600000000000009</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>45639</v>
       </c>
@@ -10808,7 +10852,7 @@
         <v>8.4877272727272732</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>45642</v>
       </c>
@@ -10843,7 +10887,7 @@
         <v>8.5154545454545456</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>45643</v>
       </c>
@@ -10878,7 +10922,7 @@
         <v>8.543181818181818</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>45644</v>
       </c>
@@ -10913,7 +10957,7 @@
         <v>8.5709090909090904</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>45645</v>
       </c>
@@ -10948,7 +10992,7 @@
         <v>8.5986363636363627</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>45646</v>
       </c>
@@ -10983,7 +11027,7 @@
         <v>8.6263636363636351</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>45649</v>
       </c>
@@ -11018,7 +11062,7 @@
         <v>8.6540909090909075</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>45650</v>
       </c>
@@ -11053,7 +11097,7 @@
         <v>8.6818181818181799</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>45651</v>
       </c>
@@ -11088,7 +11132,7 @@
         <v>8.7095454545454523</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>45652</v>
       </c>
@@ -11123,7 +11167,7 @@
         <v>8.7372727272727246</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>45653</v>
       </c>
@@ -11158,7 +11202,7 @@
         <v>8.764999999999997</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>45656</v>
       </c>
@@ -11193,7 +11237,7 @@
         <v>8.7927272727272694</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>45657</v>
       </c>
@@ -11228,7 +11272,7 @@
         <v>8.8204545454545418</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>45658</v>
       </c>
@@ -11263,7 +11307,7 @@
         <v>8.8481818181818142</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>45659</v>
       </c>
@@ -11298,7 +11342,7 @@
         <v>8.8759090909090865</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>45660</v>
       </c>
@@ -11333,7 +11377,7 @@
         <v>8.9036363636363589</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>45663</v>
       </c>
@@ -11368,7 +11412,7 @@
         <v>8.9313636363636313</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>45664</v>
       </c>
@@ -11403,7 +11447,7 @@
         <v>8.9590909090909037</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>45665</v>
       </c>
@@ -11438,7 +11482,7 @@
         <v>8.986818181818176</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>45666</v>
       </c>
@@ -11473,7 +11517,7 @@
         <v>9.0145454545454484</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>45667</v>
       </c>
@@ -11508,7 +11552,7 @@
         <v>9.0422727272727208</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>45670</v>
       </c>
@@ -11543,7 +11587,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>45671</v>
       </c>
@@ -11578,7 +11622,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>45672</v>
       </c>
@@ -11613,7 +11657,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>45673</v>
       </c>
@@ -11648,7 +11692,7 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>45674</v>
       </c>
@@ -11683,7 +11727,7 @@
         <v>8.9600000000000009</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>45677</v>
       </c>
@@ -11718,7 +11762,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>45678</v>
       </c>
@@ -11753,7 +11797,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>45679</v>
       </c>
@@ -11788,7 +11832,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>45680</v>
       </c>
@@ -11823,7 +11867,7 @@
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>45681</v>
       </c>
@@ -11858,7 +11902,7 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>45684</v>
       </c>
@@ -11893,7 +11937,7 @@
         <v>8.86</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>45685</v>
       </c>
@@ -11928,7 +11972,7 @@
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>45686</v>
       </c>
@@ -11963,7 +12007,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>45687</v>
       </c>
@@ -11998,7 +12042,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>45688</v>
       </c>
@@ -12033,7 +12077,7 @@
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>45691</v>
       </c>
@@ -12068,7 +12112,7 @@
         <v>8.85</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>45692</v>
       </c>
@@ -12103,7 +12147,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>45693</v>
       </c>
@@ -12138,7 +12182,7 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>45694</v>
       </c>
@@ -12173,7 +12217,7 @@
         <v>8.74</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>45695</v>
       </c>
@@ -12208,7 +12252,7 @@
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>45698</v>
       </c>
@@ -12243,7 +12287,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>45699</v>
       </c>
@@ -12278,7 +12322,7 @@
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>45700</v>
       </c>
@@ -12313,7 +12357,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>45701</v>
       </c>
@@ -12348,7 +12392,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>45702</v>
       </c>
@@ -12383,7 +12427,7 @@
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>45705</v>
       </c>
@@ -12418,7 +12462,7 @@
         <v>8.84</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>45706</v>
       </c>
@@ -12453,7 +12497,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>45707</v>
       </c>
@@ -12488,7 +12532,7 @@
         <v>8.9049999999999994</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>45708</v>
       </c>
@@ -12523,7 +12567,7 @@
         <v>8.94</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>45709</v>
       </c>
@@ -12558,7 +12602,7 @@
         <v>8.91</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>45712</v>
       </c>
@@ -12593,7 +12637,7 @@
         <v>8.86</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>45713</v>
       </c>
@@ -12628,7 +12672,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>45714</v>
       </c>
@@ -12663,7 +12707,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>45715</v>
       </c>
@@ -12698,7 +12742,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>45716</v>
       </c>
@@ -12733,7 +12777,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>45719</v>
       </c>
@@ -12768,7 +12812,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>45720</v>
       </c>
@@ -12803,7 +12847,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>45721</v>
       </c>
@@ -12838,7 +12882,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>45722</v>
       </c>
@@ -12873,7 +12917,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>45723</v>
       </c>
@@ -12908,7 +12952,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>45726</v>
       </c>
@@ -12943,7 +12987,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>45727</v>
       </c>
@@ -12978,7 +13022,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>45728</v>
       </c>
@@ -13013,7 +13057,7 @@
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>45729</v>
       </c>
@@ -13048,7 +13092,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>45730</v>
       </c>
@@ -13083,7 +13127,7 @@
         <v>8.86</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>45733</v>
       </c>
@@ -13118,7 +13162,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>45734</v>
       </c>
@@ -13153,7 +13197,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>45735</v>
       </c>
@@ -13188,7 +13232,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>45736</v>
       </c>
@@ -13223,7 +13267,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>45737</v>
       </c>
@@ -13258,7 +13302,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>45740</v>
       </c>
@@ -13293,7 +13337,7 @@
         <v>8.85</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>45741</v>
       </c>
@@ -13328,7 +13372,7 @@
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>45742</v>
       </c>
@@ -13363,7 +13407,7 @@
         <v>8.86</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
         <v>45743</v>
       </c>
@@ -13398,7 +13442,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
         <v>45744</v>
       </c>
@@ -13433,7 +13477,7 @@
         <v>8.91</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
         <v>45747</v>
       </c>
@@ -13468,7 +13512,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
         <v>45748</v>
       </c>
@@ -13503,7 +13547,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
         <v>45749</v>
       </c>
@@ -13538,7 +13582,7 @@
         <v>8.98</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
         <v>45750</v>
       </c>
@@ -13573,7 +13617,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A374" s="1">
         <v>45751</v>
       </c>
@@ -13608,7 +13652,7 @@
         <v>8.94</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A375" s="1">
         <v>45754</v>
       </c>
@@ -13643,7 +13687,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
         <v>45755</v>
       </c>
@@ -13678,7 +13722,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
         <v>45756</v>
       </c>
@@ -13713,7 +13757,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
         <v>45757</v>
       </c>
@@ -13748,7 +13792,7 @@
         <v>9.0299999999999994</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
         <v>45758</v>
       </c>
@@ -13783,7 +13827,7 @@
         <v>9.15</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
         <v>45761</v>
       </c>
@@ -13818,7 +13862,7 @@
         <v>9.0399999999999991</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
         <v>45762</v>
       </c>
@@ -13853,7 +13897,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
         <v>45763</v>
       </c>
@@ -13888,7 +13932,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
         <v>45764</v>
       </c>
@@ -13923,7 +13967,7 @@
         <v>9.0050000000000008</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A384" s="1">
         <v>45765</v>
       </c>
@@ -13958,7 +14002,7 @@
         <v>9.0200000000000014</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A385" s="1">
         <v>45768</v>
       </c>
@@ -13993,7 +14037,7 @@
         <v>9.0350000000000019</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
         <v>45769</v>
       </c>
@@ -14028,7 +14072,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
         <v>45770</v>
       </c>
@@ -14063,7 +14107,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A388" s="1">
         <v>45771</v>
       </c>
@@ -14098,7 +14142,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A389" s="1">
         <v>45772</v>
       </c>
@@ -14133,7 +14177,7 @@
         <v>8.8249999999999993</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
         <v>45775</v>
       </c>
@@ -14168,7 +14212,7 @@
         <v>8.84</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
         <v>45776</v>
       </c>
@@ -14203,7 +14247,7 @@
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A392" s="1">
         <v>45777</v>
       </c>
@@ -14238,7 +14282,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A393" s="1">
         <v>45778</v>
       </c>
@@ -14273,7 +14317,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
         <v>45779</v>
       </c>
@@ -14308,7 +14352,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
         <v>45782</v>
       </c>
@@ -14343,7 +14387,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A396" s="1">
         <v>45783</v>
       </c>
@@ -14378,7 +14422,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A397" s="1">
         <v>45784</v>
       </c>
@@ -14413,7 +14457,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
         <v>45785</v>
       </c>
@@ -14448,7 +14492,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
         <v>45786</v>
       </c>
@@ -14483,7 +14527,7 @@
         <v>8.74</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
         <v>45789</v>
       </c>
@@ -14518,7 +14562,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A401" s="1">
         <v>45790</v>
       </c>
@@ -14553,7 +14597,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A402" s="1">
         <v>45791</v>
       </c>
@@ -14588,7 +14632,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A403" s="1">
         <v>45792</v>
       </c>
@@ -14623,7 +14667,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A404" s="1">
         <v>45793</v>
       </c>
@@ -14658,7 +14702,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A405" s="1">
         <v>45796</v>
       </c>
@@ -14693,7 +14737,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
         <v>45797</v>
       </c>
@@ -14728,7 +14772,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
         <v>45798</v>
       </c>
@@ -14763,7 +14807,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A408" s="1">
         <v>45799</v>
       </c>
@@ -14798,7 +14842,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A409" s="1">
         <v>45800</v>
       </c>
@@ -14833,7 +14877,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
         <v>45803</v>
       </c>
@@ -14868,7 +14912,7 @@
         <v>8.7700000000000014</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
         <v>45804</v>
       </c>
@@ -14903,7 +14947,7 @@
         <v>8.74</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A412" s="1">
         <v>45805</v>
       </c>
@@ -14938,7 +14982,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A413" s="1">
         <v>45806</v>
       </c>
@@ -14973,7 +15017,7 @@
         <v>8.49</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
         <v>45807</v>
       </c>
@@ -15008,7 +15052,7 @@
         <v>8.5299999999999994</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
         <v>45810</v>
       </c>
@@ -15043,7 +15087,7 @@
         <v>8.58</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A416" s="1">
         <v>45811</v>
       </c>
@@ -15078,7 +15122,7 @@
         <v>8.5399999999999991</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A417" s="1">
         <v>45812</v>
       </c>
@@ -15113,7 +15157,7 @@
         <v>8.48</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A418" s="1">
         <v>45813</v>
       </c>
@@ -15148,7 +15192,7 @@
         <v>8.52</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A419" s="1">
         <v>45814</v>
       </c>
@@ -15183,7 +15227,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A420" s="1">
         <v>45817</v>
       </c>
@@ -15218,7 +15262,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A421" s="1">
         <v>45818</v>
       </c>
@@ -15253,7 +15297,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A422" s="1">
         <v>45819</v>
       </c>
@@ -15288,7 +15332,7 @@
         <v>8.58</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A423" s="1">
         <v>45820</v>
       </c>
@@ -15323,7 +15367,7 @@
         <v>8.58</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A424" s="1">
         <v>45821</v>
       </c>
@@ -15358,7 +15402,7 @@
         <v>8.65</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A425" s="1">
         <v>45824</v>
       </c>
@@ -15393,7 +15437,7 @@
         <v>8.65</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A426" s="1">
         <v>45825</v>
       </c>
@@ -15428,7 +15472,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
         <v>45826</v>
       </c>
@@ -15463,7 +15507,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A428" s="1">
         <v>45827</v>
       </c>
@@ -15498,7 +15542,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A429" s="1">
         <v>45828</v>
       </c>
@@ -15533,7 +15577,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
         <v>45831</v>
       </c>
@@ -15568,7 +15612,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
         <v>45832</v>
       </c>
@@ -15603,7 +15647,7 @@
         <v>8.41</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A432" s="1">
         <v>45833</v>
       </c>
@@ -15638,7 +15682,7 @@
         <v>8.43</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A433" s="1">
         <v>45834</v>
       </c>
@@ -15673,7 +15717,7 @@
         <v>8.49</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A434" s="1">
         <v>45835</v>
       </c>
@@ -15708,7 +15752,7 @@
         <v>8.49</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A435" s="1">
         <v>45838</v>
       </c>
@@ -15743,7 +15787,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A436" s="1">
         <v>45839</v>
       </c>
@@ -15778,7 +15822,7 @@
         <v>8.32</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A437" s="1">
         <v>45840</v>
       </c>
@@ -15813,7 +15857,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
         <v>45841</v>
       </c>
@@ -15848,7 +15892,7 @@
         <v>8.31</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
         <v>45842</v>
       </c>
@@ -15883,7 +15927,7 @@
         <v>8.32</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A440" s="1">
         <v>45845</v>
       </c>
@@ -15918,7 +15962,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A441" s="1">
         <v>45846</v>
       </c>
@@ -15953,7 +15997,7 @@
         <v>8.4700000000000006</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A442" s="1">
         <v>45847</v>
       </c>
@@ -15988,7 +16032,7 @@
         <v>8.41</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A443" s="1">
         <v>45848</v>
       </c>
@@ -16023,7 +16067,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A444" s="1">
         <v>45849</v>
       </c>
@@ -16058,7 +16102,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A445" s="1">
         <v>45852</v>
       </c>
@@ -16093,7 +16137,7 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A446" s="1">
         <v>45853</v>
       </c>
@@ -16128,7 +16172,7 @@
         <v>8.4700000000000006</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A447" s="1">
         <v>45854</v>
       </c>
@@ -16163,7 +16207,7 @@
         <v>8.4700000000000006</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A448" s="1">
         <v>45855</v>
       </c>
@@ -16198,7 +16242,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A449" s="1">
         <v>45856</v>
       </c>
@@ -16233,7 +16277,7 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A450" s="1">
         <v>45859</v>
       </c>
@@ -16268,7 +16312,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A451" s="1">
         <v>45860</v>
       </c>
@@ -16303,7 +16347,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A452" s="1">
         <v>45861</v>
       </c>
@@ -16338,7 +16382,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A453" s="1">
         <v>45862</v>
       </c>
@@ -16373,7 +16417,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A454" s="1">
         <v>45863</v>
       </c>
@@ -16408,7 +16452,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A455" s="1">
         <v>45866</v>
       </c>
@@ -16443,7 +16487,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A456" s="1">
         <v>45867</v>
       </c>
@@ -16478,7 +16522,7 @@
         <v>8.42</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A457" s="1">
         <v>45868</v>
       </c>
@@ -16513,7 +16557,7 @@
         <v>8.43</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
         <v>45869</v>
       </c>
@@ -16548,7 +16592,7 @@
         <v>8.2799999999999994</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
         <v>45870</v>
       </c>
@@ -16583,7 +16627,7 @@
         <v>8.23</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A460" s="1">
         <v>45873</v>
       </c>
@@ -16618,7 +16662,7 @@
         <v>8.23</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
         <v>45874</v>
       </c>
@@ -16653,7 +16697,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A462" s="1">
         <v>45875</v>
       </c>
@@ -16688,7 +16732,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A463" s="1">
         <v>45876</v>
       </c>
@@ -16723,7 +16767,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A464" s="1">
         <v>45877</v>
       </c>
@@ -16758,7 +16802,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A465" s="1">
         <v>45880</v>
       </c>
@@ -16793,7 +16837,7 @@
         <v>8.18</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A466" s="1">
         <v>45881</v>
       </c>
@@ -16828,7 +16872,7 @@
         <v>8.15</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A467" s="1">
         <v>45882</v>
       </c>
@@ -16863,7 +16907,7 @@
         <v>8.1199999999999992</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A468" s="1">
         <v>45883</v>
       </c>
@@ -16898,7 +16942,7 @@
         <v>8.14</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A469" s="1">
         <v>45884</v>
       </c>
@@ -16933,7 +16977,7 @@
         <v>8.14</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
         <v>45887</v>
       </c>
@@ -16968,7 +17012,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
         <v>45888</v>
       </c>
@@ -17003,7 +17047,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A472" s="1">
         <v>45889</v>
       </c>
@@ -17038,7 +17082,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A473" s="1">
         <v>45890</v>
       </c>
@@ -17073,7 +17117,7 @@
         <v>8.2100000000000009</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A474" s="1">
         <v>45891</v>
       </c>
@@ -17108,7 +17152,7 @@
         <v>8.14</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A475" s="1">
         <v>45894</v>
       </c>
@@ -17143,7 +17187,7 @@
         <v>8.14</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A476" s="1">
         <v>45895</v>
       </c>
@@ -17178,7 +17222,7 @@
         <v>8.18</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A477" s="1">
         <v>45896</v>
       </c>
@@ -17213,7 +17257,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A478" s="1">
         <v>45897</v>
       </c>
@@ -17248,7 +17292,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A479" s="1">
         <v>45898</v>
       </c>
@@ -17283,7 +17327,7 @@
         <v>8.18</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A480" s="1">
         <v>45901</v>
       </c>
@@ -17318,7 +17362,7 @@
         <v>8.18</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A481" s="1">
         <v>45902</v>
       </c>
@@ -17353,7 +17397,7 @@
         <v>8.24</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A482" s="1">
         <v>45903</v>
       </c>
@@ -17388,7 +17432,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A483" s="1">
         <v>45904</v>
       </c>
@@ -17423,7 +17467,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A484" s="1">
         <v>45905</v>
       </c>
@@ -17458,7 +17502,7 @@
         <v>8.14</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A485" s="1">
         <v>45908</v>
       </c>
@@ -17493,7 +17537,7 @@
         <v>8.08</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A486" s="1">
         <v>45909</v>
       </c>
@@ -17528,7 +17572,7 @@
         <v>8.08</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A487" s="1">
         <v>45910</v>
       </c>
@@ -17563,7 +17607,7 @@
         <v>8.07</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A488" s="1">
         <v>45911</v>
       </c>
@@ -17598,7 +17642,7 @@
         <v>8.0449999999999999</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A489" s="1">
         <v>45912</v>
       </c>
@@ -17633,7 +17677,7 @@
         <v>8.02</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A490" s="1">
         <v>45915</v>
       </c>
@@ -17668,7 +17712,7 @@
         <v>7.95</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
         <v>45916</v>
       </c>
@@ -17703,7 +17747,7 @@
         <v>7.95</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A492" s="1">
         <v>45917</v>
       </c>
@@ -17738,7 +17782,7 @@
         <v>7.89</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A493" s="1">
         <v>45918</v>
       </c>
@@ -17773,7 +17817,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
         <v>45919</v>
       </c>
@@ -17808,7 +17852,7 @@
         <v>7.97</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
         <v>45922</v>
       </c>
@@ -17843,7 +17887,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A496" s="1">
         <v>45923</v>
       </c>
@@ -17878,7 +17922,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A497" s="1">
         <v>45924</v>
       </c>
@@ -17913,7 +17957,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A498" s="1">
         <v>45925</v>
       </c>
@@ -17948,7 +17992,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A499" s="1">
         <v>45926</v>
       </c>
@@ -17983,7 +18027,7 @@
         <v>8.0299999999999994</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A500" s="1">
         <v>45929</v>
       </c>
@@ -18018,7 +18062,7 @@
         <v>8.0299999999999994</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A501" s="1">
         <v>45930</v>
       </c>
@@ -18053,7 +18097,7 @@
         <v>8.01</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A502" s="1">
         <v>45931</v>
       </c>
@@ -18088,7 +18132,7 @@
         <v>7.98</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A503" s="1">
         <v>45932</v>
       </c>
@@ -18123,7 +18167,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A504" s="1">
         <v>45933</v>
       </c>
@@ -18158,7 +18202,7 @@
         <v>7.93</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A505" s="1">
         <v>45936</v>
       </c>
@@ -18193,7 +18237,7 @@
         <v>7.98</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A506" s="1">
         <v>45937</v>
       </c>
@@ -18228,7 +18272,7 @@
         <v>7.9600000000000009</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
         <v>45938</v>
       </c>
@@ -18263,7 +18307,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A508" s="1">
         <v>45939</v>
       </c>
@@ -18298,7 +18342,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
         <v>45940</v>
       </c>
@@ -18333,7 +18377,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
         <v>45943</v>
       </c>
@@ -18368,7 +18412,7 @@
         <v>7.95</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
         <v>45944</v>
       </c>
@@ -18403,7 +18447,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A512" s="1">
         <v>45945</v>
       </c>
@@ -18438,7 +18482,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A513" s="1">
         <v>45946</v>
       </c>
@@ -18473,7 +18517,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A514" s="1">
         <v>45947</v>
       </c>
@@ -18508,7 +18552,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A515" s="1">
         <v>45950</v>
       </c>
@@ -18543,7 +18587,7 @@
         <v>7.78</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
         <v>45951</v>
       </c>
@@ -18578,7 +18622,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
         <v>45952</v>
       </c>
@@ -18613,7 +18657,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
         <v>45953</v>
       </c>
@@ -18648,7 +18692,7 @@
         <v>7.8049999999999997</v>
       </c>
     </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
         <v>45954</v>
       </c>
@@ -18683,7 +18727,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
         <v>45957</v>
       </c>
@@ -18718,7 +18762,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
         <v>45958</v>
       </c>
@@ -18753,7 +18797,7 @@
         <v>7.79</v>
       </c>
     </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
         <v>45959</v>
       </c>
@@ -18788,7 +18832,7 @@
         <v>7.77</v>
       </c>
     </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
         <v>45960</v>
       </c>
@@ -18823,7 +18867,7 @@
         <v>7.82</v>
       </c>
     </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A524" s="1">
         <v>45961</v>
       </c>
@@ -18858,7 +18902,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
         <v>45964</v>
       </c>
@@ -18893,7 +18937,7 @@
         <v>7.79</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A526" s="1">
         <v>45965</v>
       </c>
@@ -18928,7 +18972,7 @@
         <v>7.78</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A527" s="1">
         <v>45966</v>
       </c>
@@ -18963,7 +19007,7 @@
         <v>7.77</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A528" s="1">
         <v>45967</v>
       </c>
@@ -18998,7 +19042,7 @@
         <v>7.76</v>
       </c>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A529" s="1">
         <v>45968</v>
       </c>
@@ -19033,7 +19077,7 @@
         <v>7.78</v>
       </c>
     </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A530" s="1">
         <v>45971</v>
       </c>
@@ -19068,7 +19112,7 @@
         <v>7.73</v>
       </c>
     </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A531" s="1">
         <v>45972</v>
       </c>
@@ -19103,7 +19147,7 @@
         <v>7.74</v>
       </c>
     </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A532" s="1">
         <v>45973</v>
       </c>
@@ -19138,7 +19182,7 @@
         <v>7.64</v>
       </c>
     </row>
-    <row r="533" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A533" s="1">
         <v>45974</v>
       </c>
@@ -19173,7 +19217,7 @@
         <v>7.59</v>
       </c>
     </row>
-    <row r="534" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A534" s="1">
         <v>45975</v>
       </c>
@@ -19208,7 +19252,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="535" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A535" s="1">
         <v>45978</v>
       </c>
@@ -19243,7 +19287,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A536" s="1">
         <v>45979</v>
       </c>
@@ -19278,7 +19322,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="537" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A537" s="1">
         <v>45980</v>
       </c>
@@ -19313,7 +19357,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A538" s="1">
         <v>45981</v>
       </c>
@@ -19348,7 +19392,7 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A539" s="1">
         <v>45982</v>
       </c>
@@ -19383,7 +19427,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A540" s="1">
         <v>45985</v>
       </c>
@@ -19418,7 +19462,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A541" s="1">
         <v>45986</v>
       </c>
@@ -19453,7 +19497,7 @@
         <v>7.53</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A542" s="1">
         <v>45987</v>
       </c>
@@ -19488,7 +19532,7 @@
         <v>7.53</v>
       </c>
     </row>
-    <row r="543" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A543" s="1">
         <v>45988</v>
       </c>
@@ -19523,7 +19567,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A544" s="1">
         <v>45989</v>
       </c>
@@ -19558,7 +19602,7 @@
         <v>7.51</v>
       </c>
     </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A545" s="1">
         <v>45992</v>
       </c>
@@ -19593,7 +19637,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A546" s="1">
         <v>45993</v>
       </c>
@@ -19628,7 +19672,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A547" s="1">
         <v>45994</v>
       </c>
@@ -19663,7 +19707,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A548" s="1">
         <v>45995</v>
       </c>
@@ -19696,6 +19740,2911 @@
       </c>
       <c r="K548" s="5">
         <v>7.52</v>
+      </c>
+    </row>
+    <row r="549" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A549" s="13">
+        <v>45996</v>
+      </c>
+      <c r="B549" s="14">
+        <v>6.78</v>
+      </c>
+      <c r="C549" s="14">
+        <v>6.6783333333333328</v>
+      </c>
+      <c r="D549" s="14">
+        <v>6.5108333333333333</v>
+      </c>
+      <c r="E549" s="14">
+        <v>6.4241666666666664</v>
+      </c>
+      <c r="F549" s="15">
+        <v>6.5983095407645465</v>
+      </c>
+      <c r="G549" s="14">
+        <v>6.2933333333333339</v>
+      </c>
+      <c r="H549" s="14">
+        <v>6.4558333333333335</v>
+      </c>
+      <c r="I549" s="14">
+        <v>6.47</v>
+      </c>
+      <c r="J549" s="14">
+        <v>6.7133333333333338</v>
+      </c>
+      <c r="K549" s="14">
+        <v>7.5316666666666663</v>
+      </c>
+    </row>
+    <row r="550" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A550" s="13">
+        <v>45999</v>
+      </c>
+      <c r="B550" s="14">
+        <v>6.78</v>
+      </c>
+      <c r="C550" s="14">
+        <v>6.6766666666666659</v>
+      </c>
+      <c r="D550" s="14">
+        <v>6.5116666666666667</v>
+      </c>
+      <c r="E550" s="14">
+        <v>6.4283333333333328</v>
+      </c>
+      <c r="F550" s="15">
+        <v>6.5991434416927675</v>
+      </c>
+      <c r="G550" s="14">
+        <v>6.3066666666666675</v>
+      </c>
+      <c r="H550" s="14">
+        <v>6.4616666666666669</v>
+      </c>
+      <c r="I550" s="14">
+        <v>6.4799999999999995</v>
+      </c>
+      <c r="J550" s="14">
+        <v>6.7266666666666675</v>
+      </c>
+      <c r="K550" s="14">
+        <v>7.543333333333333</v>
+      </c>
+    </row>
+    <row r="551" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A551" s="13">
+        <v>46000</v>
+      </c>
+      <c r="B551" s="14">
+        <v>6.78</v>
+      </c>
+      <c r="C551" s="14">
+        <v>6.6749999999999989</v>
+      </c>
+      <c r="D551" s="14">
+        <v>6.5125000000000002</v>
+      </c>
+      <c r="E551" s="14">
+        <v>6.4324999999999992</v>
+      </c>
+      <c r="F551" s="15">
+        <v>6.5999773315133403</v>
+      </c>
+      <c r="G551" s="14">
+        <v>6.3200000000000012</v>
+      </c>
+      <c r="H551" s="14">
+        <v>6.4675000000000002</v>
+      </c>
+      <c r="I551" s="14">
+        <v>6.4899999999999993</v>
+      </c>
+      <c r="J551" s="14">
+        <v>6.7400000000000011</v>
+      </c>
+      <c r="K551" s="14">
+        <v>7.5549999999999997</v>
+      </c>
+    </row>
+    <row r="552" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A552" s="13">
+        <v>46001</v>
+      </c>
+      <c r="B552" s="14">
+        <v>6.78</v>
+      </c>
+      <c r="C552" s="14">
+        <v>6.673333333333332</v>
+      </c>
+      <c r="D552" s="14">
+        <v>6.5133333333333336</v>
+      </c>
+      <c r="E552" s="14">
+        <v>6.4366666666666656</v>
+      </c>
+      <c r="F552" s="15">
+        <v>6.600811210226265</v>
+      </c>
+      <c r="G552" s="14">
+        <v>6.3333333333333348</v>
+      </c>
+      <c r="H552" s="14">
+        <v>6.4733333333333336</v>
+      </c>
+      <c r="I552" s="14">
+        <v>6.4999999999999991</v>
+      </c>
+      <c r="J552" s="14">
+        <v>6.7533333333333347</v>
+      </c>
+      <c r="K552" s="14">
+        <v>7.5666666666666664</v>
+      </c>
+    </row>
+    <row r="553" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A553" s="13">
+        <v>46002</v>
+      </c>
+      <c r="B553" s="14">
+        <v>6.78</v>
+      </c>
+      <c r="C553" s="14">
+        <v>6.6716666666666651</v>
+      </c>
+      <c r="D553" s="14">
+        <v>6.5141666666666671</v>
+      </c>
+      <c r="E553" s="14">
+        <v>6.4408333333333321</v>
+      </c>
+      <c r="F553" s="15">
+        <v>6.6016450778315416</v>
+      </c>
+      <c r="G553" s="14">
+        <v>6.3466666666666685</v>
+      </c>
+      <c r="H553" s="14">
+        <v>6.479166666666667</v>
+      </c>
+      <c r="I553" s="14">
+        <v>6.5099999999999989</v>
+      </c>
+      <c r="J553" s="14">
+        <v>6.7666666666666684</v>
+      </c>
+      <c r="K553" s="14">
+        <v>7.5783333333333331</v>
+      </c>
+    </row>
+    <row r="554" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A554" s="13">
+        <v>46003</v>
+      </c>
+      <c r="B554" s="14">
+        <v>6.78</v>
+      </c>
+      <c r="C554" s="14">
+        <v>6.6699999999999982</v>
+      </c>
+      <c r="D554" s="14">
+        <v>6.5150000000000006</v>
+      </c>
+      <c r="E554" s="14">
+        <v>6.4449999999999985</v>
+      </c>
+      <c r="F554" s="15">
+        <v>6.6024789343296142</v>
+      </c>
+      <c r="G554" s="14">
+        <v>6.3600000000000021</v>
+      </c>
+      <c r="H554" s="14">
+        <v>6.4850000000000003</v>
+      </c>
+      <c r="I554" s="14">
+        <v>6.5199999999999987</v>
+      </c>
+      <c r="J554" s="14">
+        <v>6.780000000000002</v>
+      </c>
+      <c r="K554" s="14">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="555" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A555" s="13">
+        <v>46006</v>
+      </c>
+      <c r="B555" s="14">
+        <v>6.78</v>
+      </c>
+      <c r="C555" s="14">
+        <v>6.67</v>
+      </c>
+      <c r="D555" s="14">
+        <v>6.5149999999999997</v>
+      </c>
+      <c r="E555" s="14">
+        <v>6.4450000000000003</v>
+      </c>
+      <c r="F555" s="15">
+        <v>6.6024789343296142</v>
+      </c>
+      <c r="G555" s="14">
+        <v>6.36</v>
+      </c>
+      <c r="H555" s="14">
+        <v>6.4850000000000003</v>
+      </c>
+      <c r="I555" s="14">
+        <v>6.52</v>
+      </c>
+      <c r="J555" s="14">
+        <v>6.78</v>
+      </c>
+      <c r="K555" s="14">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="556" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A556" s="13">
+        <v>46007</v>
+      </c>
+      <c r="B556" s="14">
+        <v>6.78</v>
+      </c>
+      <c r="C556" s="14">
+        <v>6.67</v>
+      </c>
+      <c r="D556" s="14">
+        <v>6.5149999999999997</v>
+      </c>
+      <c r="E556" s="14">
+        <v>6.4450000000000003</v>
+      </c>
+      <c r="F556" s="15">
+        <v>6.6024789343296142</v>
+      </c>
+      <c r="G556" s="14">
+        <v>6.36</v>
+      </c>
+      <c r="H556" s="14">
+        <v>6.4850000000000003</v>
+      </c>
+      <c r="I556" s="14">
+        <v>6.52</v>
+      </c>
+      <c r="J556" s="14">
+        <v>6.78</v>
+      </c>
+      <c r="K556" s="14">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="557" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A557" s="13">
+        <v>46008</v>
+      </c>
+      <c r="B557" s="14">
+        <v>6.7773684210526319</v>
+      </c>
+      <c r="C557" s="14">
+        <v>6.662105263157895</v>
+      </c>
+      <c r="D557" s="14">
+        <v>6.5084210526315784</v>
+      </c>
+      <c r="E557" s="14">
+        <v>6.4347368421052638</v>
+      </c>
+      <c r="F557" s="15">
+        <v>6.5956359167742518</v>
+      </c>
+      <c r="G557" s="14">
+        <v>6.350526315789474</v>
+      </c>
+      <c r="H557" s="14">
+        <v>6.4768421052631586</v>
+      </c>
+      <c r="I557" s="14">
+        <v>6.5110526315789468</v>
+      </c>
+      <c r="J557" s="14">
+        <v>6.7700000000000005</v>
+      </c>
+      <c r="K557" s="14">
+        <v>7.5794736842105266</v>
+      </c>
+    </row>
+    <row r="558" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A558" s="13">
+        <v>46009</v>
+      </c>
+      <c r="B558" s="14">
+        <v>6.7747368421052636</v>
+      </c>
+      <c r="C558" s="14">
+        <v>6.65421052631579</v>
+      </c>
+      <c r="D558" s="14">
+        <v>6.5018421052631572</v>
+      </c>
+      <c r="E558" s="14">
+        <v>6.4244736842105272</v>
+      </c>
+      <c r="F558" s="15">
+        <v>6.5887928992188893</v>
+      </c>
+      <c r="G558" s="14">
+        <v>6.3410526315789477</v>
+      </c>
+      <c r="H558" s="14">
+        <v>6.4686842105263169</v>
+      </c>
+      <c r="I558" s="14">
+        <v>6.5021052631578939</v>
+      </c>
+      <c r="J558" s="14">
+        <v>6.7600000000000007</v>
+      </c>
+      <c r="K558" s="14">
+        <v>7.5689473684210533</v>
+      </c>
+    </row>
+    <row r="559" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A559" s="13">
+        <v>46010</v>
+      </c>
+      <c r="B559" s="14">
+        <v>6.7721052631578953</v>
+      </c>
+      <c r="C559" s="14">
+        <v>6.6463157894736851</v>
+      </c>
+      <c r="D559" s="14">
+        <v>6.495263157894736</v>
+      </c>
+      <c r="E559" s="14">
+        <v>6.4142105263157907</v>
+      </c>
+      <c r="F559" s="15">
+        <v>6.5819498816635269</v>
+      </c>
+      <c r="G559" s="14">
+        <v>6.3315789473684214</v>
+      </c>
+      <c r="H559" s="14">
+        <v>6.4605263157894752</v>
+      </c>
+      <c r="I559" s="14">
+        <v>6.4931578947368411</v>
+      </c>
+      <c r="J559" s="14">
+        <v>6.7500000000000009</v>
+      </c>
+      <c r="K559" s="14">
+        <v>7.55842105263158</v>
+      </c>
+    </row>
+    <row r="560" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A560" s="13">
+        <v>46013</v>
+      </c>
+      <c r="B560" s="14">
+        <v>6.769473684210527</v>
+      </c>
+      <c r="C560" s="14">
+        <v>6.6384210526315801</v>
+      </c>
+      <c r="D560" s="14">
+        <v>6.4886842105263147</v>
+      </c>
+      <c r="E560" s="14">
+        <v>6.4039473684210542</v>
+      </c>
+      <c r="F560" s="15">
+        <v>6.5751068641081645</v>
+      </c>
+      <c r="G560" s="14">
+        <v>6.3221052631578951</v>
+      </c>
+      <c r="H560" s="14">
+        <v>6.4523684210526335</v>
+      </c>
+      <c r="I560" s="14">
+        <v>6.4842105263157883</v>
+      </c>
+      <c r="J560" s="14">
+        <v>6.7400000000000011</v>
+      </c>
+      <c r="K560" s="14">
+        <v>7.5478947368421068</v>
+      </c>
+    </row>
+    <row r="561" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A561" s="13">
+        <v>46014</v>
+      </c>
+      <c r="B561" s="14">
+        <v>6.7668421052631587</v>
+      </c>
+      <c r="C561" s="14">
+        <v>6.6305263157894752</v>
+      </c>
+      <c r="D561" s="14">
+        <v>6.4821052631578935</v>
+      </c>
+      <c r="E561" s="14">
+        <v>6.3936842105263176</v>
+      </c>
+      <c r="F561" s="15">
+        <v>6.568263846552802</v>
+      </c>
+      <c r="G561" s="14">
+        <v>6.3126315789473688</v>
+      </c>
+      <c r="H561" s="14">
+        <v>6.4442105263157918</v>
+      </c>
+      <c r="I561" s="14">
+        <v>6.4752631578947355</v>
+      </c>
+      <c r="J561" s="14">
+        <v>6.7300000000000013</v>
+      </c>
+      <c r="K561" s="14">
+        <v>7.5373684210526335</v>
+      </c>
+    </row>
+    <row r="562" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A562" s="13">
+        <v>46015</v>
+      </c>
+      <c r="B562" s="14">
+        <v>6.7642105263157903</v>
+      </c>
+      <c r="C562" s="14">
+        <v>6.6226315789473702</v>
+      </c>
+      <c r="D562" s="14">
+        <v>6.4755263157894722</v>
+      </c>
+      <c r="E562" s="14">
+        <v>6.3834210526315811</v>
+      </c>
+      <c r="F562" s="15">
+        <v>6.5614208289974396</v>
+      </c>
+      <c r="G562" s="14">
+        <v>6.3031578947368425</v>
+      </c>
+      <c r="H562" s="14">
+        <v>6.4360526315789501</v>
+      </c>
+      <c r="I562" s="14">
+        <v>6.4663157894736827</v>
+      </c>
+      <c r="J562" s="14">
+        <v>6.7200000000000015</v>
+      </c>
+      <c r="K562" s="14">
+        <v>7.5268421052631602</v>
+      </c>
+    </row>
+    <row r="563" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A563" s="13">
+        <v>46016</v>
+      </c>
+      <c r="B563" s="14">
+        <v>6.761578947368422</v>
+      </c>
+      <c r="C563" s="14">
+        <v>6.6147368421052652</v>
+      </c>
+      <c r="D563" s="14">
+        <v>6.468947368421051</v>
+      </c>
+      <c r="E563" s="14">
+        <v>6.3731578947368446</v>
+      </c>
+      <c r="F563" s="15">
+        <v>6.5545778114420772</v>
+      </c>
+      <c r="G563" s="14">
+        <v>6.2936842105263162</v>
+      </c>
+      <c r="H563" s="14">
+        <v>6.4278947368421084</v>
+      </c>
+      <c r="I563" s="14">
+        <v>6.4573684210526299</v>
+      </c>
+      <c r="J563" s="14">
+        <v>6.7100000000000017</v>
+      </c>
+      <c r="K563" s="14">
+        <v>7.5163157894736869</v>
+      </c>
+    </row>
+    <row r="564" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A564" s="13">
+        <v>46017</v>
+      </c>
+      <c r="B564" s="14">
+        <v>6.7589473684210537</v>
+      </c>
+      <c r="C564" s="14">
+        <v>6.6068421052631603</v>
+      </c>
+      <c r="D564" s="14">
+        <v>6.4623684210526298</v>
+      </c>
+      <c r="E564" s="14">
+        <v>6.362894736842108</v>
+      </c>
+      <c r="F564" s="15">
+        <v>6.5477347938867148</v>
+      </c>
+      <c r="G564" s="14">
+        <v>6.2842105263157899</v>
+      </c>
+      <c r="H564" s="14">
+        <v>6.4197368421052667</v>
+      </c>
+      <c r="I564" s="14">
+        <v>6.4484210526315771</v>
+      </c>
+      <c r="J564" s="14">
+        <v>6.700000000000002</v>
+      </c>
+      <c r="K564" s="14">
+        <v>7.5057894736842137</v>
+      </c>
+    </row>
+    <row r="565" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A565" s="13">
+        <v>46020</v>
+      </c>
+      <c r="B565" s="14">
+        <v>6.7563157894736854</v>
+      </c>
+      <c r="C565" s="14">
+        <v>6.5989473684210553</v>
+      </c>
+      <c r="D565" s="14">
+        <v>6.4557894736842085</v>
+      </c>
+      <c r="E565" s="14">
+        <v>6.3526315789473715</v>
+      </c>
+      <c r="F565" s="15">
+        <v>6.5408917763313523</v>
+      </c>
+      <c r="G565" s="14">
+        <v>6.2747368421052636</v>
+      </c>
+      <c r="H565" s="14">
+        <v>6.411578947368425</v>
+      </c>
+      <c r="I565" s="14">
+        <v>6.4394736842105242</v>
+      </c>
+      <c r="J565" s="14">
+        <v>6.6900000000000022</v>
+      </c>
+      <c r="K565" s="14">
+        <v>7.4952631578947404</v>
+      </c>
+    </row>
+    <row r="566" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A566" s="13">
+        <v>46021</v>
+      </c>
+      <c r="B566" s="14">
+        <v>6.7536842105263171</v>
+      </c>
+      <c r="C566" s="14">
+        <v>6.5910526315789504</v>
+      </c>
+      <c r="D566" s="14">
+        <v>6.4492105263157873</v>
+      </c>
+      <c r="E566" s="14">
+        <v>6.342368421052635</v>
+      </c>
+      <c r="F566" s="15">
+        <v>6.5340487587759899</v>
+      </c>
+      <c r="G566" s="14">
+        <v>6.2652631578947373</v>
+      </c>
+      <c r="H566" s="14">
+        <v>6.4034210526315833</v>
+      </c>
+      <c r="I566" s="14">
+        <v>6.4305263157894714</v>
+      </c>
+      <c r="J566" s="14">
+        <v>6.6800000000000024</v>
+      </c>
+      <c r="K566" s="14">
+        <v>7.4847368421052671</v>
+      </c>
+    </row>
+    <row r="567" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A567" s="13">
+        <v>46022</v>
+      </c>
+      <c r="B567" s="14">
+        <v>6.7510526315789487</v>
+      </c>
+      <c r="C567" s="14">
+        <v>6.5831578947368454</v>
+      </c>
+      <c r="D567" s="14">
+        <v>6.442631578947366</v>
+      </c>
+      <c r="E567" s="14">
+        <v>6.3321052631578985</v>
+      </c>
+      <c r="F567" s="15">
+        <v>6.5272057412206275</v>
+      </c>
+      <c r="G567" s="14">
+        <v>6.255789473684211</v>
+      </c>
+      <c r="H567" s="14">
+        <v>6.3952631578947416</v>
+      </c>
+      <c r="I567" s="14">
+        <v>6.4215789473684186</v>
+      </c>
+      <c r="J567" s="14">
+        <v>6.6700000000000026</v>
+      </c>
+      <c r="K567" s="14">
+        <v>7.4742105263157939</v>
+      </c>
+    </row>
+    <row r="568" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A568" s="13">
+        <v>46023</v>
+      </c>
+      <c r="B568" s="14">
+        <v>6.7484210526315804</v>
+      </c>
+      <c r="C568" s="14">
+        <v>6.5752631578947405</v>
+      </c>
+      <c r="D568" s="14">
+        <v>6.4360526315789448</v>
+      </c>
+      <c r="E568" s="14">
+        <v>6.3218421052631619</v>
+      </c>
+      <c r="F568" s="15">
+        <v>6.520362723665265</v>
+      </c>
+      <c r="G568" s="14">
+        <v>6.2463157894736847</v>
+      </c>
+      <c r="H568" s="14">
+        <v>6.3871052631578999</v>
+      </c>
+      <c r="I568" s="14">
+        <v>6.4126315789473658</v>
+      </c>
+      <c r="J568" s="14">
+        <v>6.6600000000000028</v>
+      </c>
+      <c r="K568" s="14">
+        <v>7.4636842105263206</v>
+      </c>
+    </row>
+    <row r="569" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A569" s="13">
+        <v>46024</v>
+      </c>
+      <c r="B569" s="14">
+        <v>6.7457894736842121</v>
+      </c>
+      <c r="C569" s="14">
+        <v>6.5673684210526355</v>
+      </c>
+      <c r="D569" s="14">
+        <v>6.4294736842105236</v>
+      </c>
+      <c r="E569" s="14">
+        <v>6.3115789473684254</v>
+      </c>
+      <c r="F569" s="15">
+        <v>6.5135197061099026</v>
+      </c>
+      <c r="G569" s="14">
+        <v>6.2368421052631584</v>
+      </c>
+      <c r="H569" s="14">
+        <v>6.3789473684210583</v>
+      </c>
+      <c r="I569" s="14">
+        <v>6.403684210526313</v>
+      </c>
+      <c r="J569" s="14">
+        <v>6.650000000000003</v>
+      </c>
+      <c r="K569" s="14">
+        <v>7.4531578947368473</v>
+      </c>
+    </row>
+    <row r="570" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A570" s="13">
+        <v>46027</v>
+      </c>
+      <c r="B570" s="14">
+        <v>6.7431578947368438</v>
+      </c>
+      <c r="C570" s="14">
+        <v>6.5594736842105306</v>
+      </c>
+      <c r="D570" s="14">
+        <v>6.4228947368421023</v>
+      </c>
+      <c r="E570" s="14">
+        <v>6.3013157894736889</v>
+      </c>
+      <c r="F570" s="15">
+        <v>6.5066766885545402</v>
+      </c>
+      <c r="G570" s="14">
+        <v>6.2273684210526321</v>
+      </c>
+      <c r="H570" s="14">
+        <v>6.3707894736842166</v>
+      </c>
+      <c r="I570" s="14">
+        <v>6.3947368421052602</v>
+      </c>
+      <c r="J570" s="14">
+        <v>6.6400000000000032</v>
+      </c>
+      <c r="K570" s="14">
+        <v>7.442631578947374</v>
+      </c>
+    </row>
+    <row r="571" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A571" s="13">
+        <v>46028</v>
+      </c>
+      <c r="B571" s="14">
+        <v>6.7405263157894755</v>
+      </c>
+      <c r="C571" s="14">
+        <v>6.5515789473684256</v>
+      </c>
+      <c r="D571" s="14">
+        <v>6.4163157894736811</v>
+      </c>
+      <c r="E571" s="14">
+        <v>6.2910526315789523</v>
+      </c>
+      <c r="F571" s="15">
+        <v>6.4998336709991777</v>
+      </c>
+      <c r="G571" s="14">
+        <v>6.2178947368421058</v>
+      </c>
+      <c r="H571" s="14">
+        <v>6.3626315789473749</v>
+      </c>
+      <c r="I571" s="14">
+        <v>6.3857894736842074</v>
+      </c>
+      <c r="J571" s="14">
+        <v>6.6300000000000034</v>
+      </c>
+      <c r="K571" s="14">
+        <v>7.4321052631579008</v>
+      </c>
+    </row>
+    <row r="572" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A572" s="13">
+        <v>46029</v>
+      </c>
+      <c r="B572" s="14">
+        <v>6.7378947368421072</v>
+      </c>
+      <c r="C572" s="14">
+        <v>6.5436842105263207</v>
+      </c>
+      <c r="D572" s="14">
+        <v>6.4097368421052598</v>
+      </c>
+      <c r="E572" s="14">
+        <v>6.2807894736842158</v>
+      </c>
+      <c r="F572" s="15">
+        <v>6.4929906534438153</v>
+      </c>
+      <c r="G572" s="14">
+        <v>6.2084210526315795</v>
+      </c>
+      <c r="H572" s="14">
+        <v>6.3544736842105332</v>
+      </c>
+      <c r="I572" s="14">
+        <v>6.3768421052631545</v>
+      </c>
+      <c r="J572" s="14">
+        <v>6.6200000000000037</v>
+      </c>
+      <c r="K572" s="14">
+        <v>7.4215789473684275</v>
+      </c>
+    </row>
+    <row r="573" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A573" s="13">
+        <v>46030</v>
+      </c>
+      <c r="B573" s="14">
+        <v>6.7352631578947388</v>
+      </c>
+      <c r="C573" s="14">
+        <v>6.5357894736842157</v>
+      </c>
+      <c r="D573" s="14">
+        <v>6.4031578947368386</v>
+      </c>
+      <c r="E573" s="14">
+        <v>6.2705263157894793</v>
+      </c>
+      <c r="F573" s="15">
+        <v>6.4861476358884529</v>
+      </c>
+      <c r="G573" s="14">
+        <v>6.1989473684210532</v>
+      </c>
+      <c r="H573" s="14">
+        <v>6.3463157894736915</v>
+      </c>
+      <c r="I573" s="14">
+        <v>6.3678947368421017</v>
+      </c>
+      <c r="J573" s="14">
+        <v>6.6100000000000039</v>
+      </c>
+      <c r="K573" s="14">
+        <v>7.4110526315789542</v>
+      </c>
+    </row>
+    <row r="574" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A574" s="13">
+        <v>46031</v>
+      </c>
+      <c r="B574" s="14">
+        <v>6.7326315789473705</v>
+      </c>
+      <c r="C574" s="14">
+        <v>6.5278947368421107</v>
+      </c>
+      <c r="D574" s="14">
+        <v>6.3965789473684174</v>
+      </c>
+      <c r="E574" s="14">
+        <v>6.2602631578947427</v>
+      </c>
+      <c r="F574" s="15">
+        <v>6.4793046183330905</v>
+      </c>
+      <c r="G574" s="14">
+        <v>6.1894736842105269</v>
+      </c>
+      <c r="H574" s="14">
+        <v>6.3381578947368498</v>
+      </c>
+      <c r="I574" s="14">
+        <v>6.3589473684210489</v>
+      </c>
+      <c r="J574" s="14">
+        <v>6.6000000000000041</v>
+      </c>
+      <c r="K574" s="14">
+        <v>7.4005263157894809</v>
+      </c>
+    </row>
+    <row r="575" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A575" s="13">
+        <v>46034</v>
+      </c>
+      <c r="B575" s="14">
+        <v>6.73</v>
+      </c>
+      <c r="C575" s="14">
+        <v>6.52</v>
+      </c>
+      <c r="D575" s="14">
+        <v>6.39</v>
+      </c>
+      <c r="E575" s="14">
+        <v>6.25</v>
+      </c>
+      <c r="F575" s="15">
+        <v>6.4724616007777236</v>
+      </c>
+      <c r="G575" s="14">
+        <v>6.18</v>
+      </c>
+      <c r="H575" s="14">
+        <v>6.33</v>
+      </c>
+      <c r="I575" s="14">
+        <v>6.35</v>
+      </c>
+      <c r="J575" s="14">
+        <v>6.59</v>
+      </c>
+      <c r="K575" s="14">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="576" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A576" s="13">
+        <v>46035</v>
+      </c>
+      <c r="B576" s="14">
+        <v>6.73</v>
+      </c>
+      <c r="C576" s="14">
+        <v>6.53</v>
+      </c>
+      <c r="D576" s="14">
+        <v>6.38</v>
+      </c>
+      <c r="E576" s="14">
+        <v>6.24</v>
+      </c>
+      <c r="F576" s="15">
+        <v>6.4699593475577188</v>
+      </c>
+      <c r="G576" s="14">
+        <v>6.18</v>
+      </c>
+      <c r="H576" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="I576" s="14">
+        <v>6.36</v>
+      </c>
+      <c r="J576" s="14">
+        <v>6.59</v>
+      </c>
+      <c r="K576" s="14">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="577" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A577" s="13">
+        <v>46036</v>
+      </c>
+      <c r="B577" s="14">
+        <v>6.73</v>
+      </c>
+      <c r="C577" s="14">
+        <v>6.55</v>
+      </c>
+      <c r="D577" s="14">
+        <v>6.43</v>
+      </c>
+      <c r="E577" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="F577" s="15">
+        <v>6.5024691669281154</v>
+      </c>
+      <c r="G577" s="14">
+        <v>6.25</v>
+      </c>
+      <c r="H577" s="14">
+        <v>6.37</v>
+      </c>
+      <c r="I577" s="14">
+        <v>6.39</v>
+      </c>
+      <c r="J577" s="14">
+        <v>6.63</v>
+      </c>
+      <c r="K577" s="14">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="578" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A578" s="13">
+        <v>46037</v>
+      </c>
+      <c r="B578" s="14">
+        <v>6.73</v>
+      </c>
+      <c r="C578" s="14">
+        <v>6.56</v>
+      </c>
+      <c r="D578" s="14">
+        <v>6.43</v>
+      </c>
+      <c r="E578" s="14">
+        <v>6.29</v>
+      </c>
+      <c r="F578" s="15">
+        <v>6.5024675673120313</v>
+      </c>
+      <c r="G578" s="14">
+        <v>6.23</v>
+      </c>
+      <c r="H578" s="14">
+        <v>6.37</v>
+      </c>
+      <c r="I578" s="14">
+        <v>6.4</v>
+      </c>
+      <c r="J578" s="14">
+        <v>6.63</v>
+      </c>
+      <c r="K578" s="14">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="579" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A579" s="13">
+        <v>46038</v>
+      </c>
+      <c r="B579" s="14">
+        <v>6.73</v>
+      </c>
+      <c r="C579" s="14">
+        <v>6.56</v>
+      </c>
+      <c r="D579" s="14">
+        <v>6.43</v>
+      </c>
+      <c r="E579" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="F579" s="15">
+        <v>6.5049688515895987</v>
+      </c>
+      <c r="G579" s="14">
+        <v>6.26</v>
+      </c>
+      <c r="H579" s="14">
+        <v>6.39</v>
+      </c>
+      <c r="I579" s="14">
+        <v>6.42</v>
+      </c>
+      <c r="J579" s="14">
+        <v>6.67</v>
+      </c>
+      <c r="K579" s="14">
+        <v>7.47</v>
+      </c>
+    </row>
+    <row r="580" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A580" s="13">
+        <v>46041</v>
+      </c>
+      <c r="B580" s="14">
+        <v>6.73</v>
+      </c>
+      <c r="C580" s="14">
+        <v>6.57</v>
+      </c>
+      <c r="D580" s="14">
+        <v>6.44</v>
+      </c>
+      <c r="E580" s="14">
+        <v>6.28</v>
+      </c>
+      <c r="F580" s="15">
+        <v>6.5049662673241748</v>
+      </c>
+      <c r="G580" s="14">
+        <v>6.26</v>
+      </c>
+      <c r="H580" s="14">
+        <v>6.39</v>
+      </c>
+      <c r="I580" s="14">
+        <v>6.43</v>
+      </c>
+      <c r="J580" s="14">
+        <v>6.69</v>
+      </c>
+      <c r="K580" s="14">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="581" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A581" s="13">
+        <v>46042</v>
+      </c>
+      <c r="B581" s="14">
+        <v>6.73</v>
+      </c>
+      <c r="C581" s="14">
+        <v>6.56</v>
+      </c>
+      <c r="D581" s="14">
+        <v>6.44</v>
+      </c>
+      <c r="E581" s="14">
+        <v>6.31</v>
+      </c>
+      <c r="F581" s="15">
+        <v>6.5099705431528321</v>
+      </c>
+      <c r="G581" s="14">
+        <v>6.28</v>
+      </c>
+      <c r="H581" s="14">
+        <v>6.38</v>
+      </c>
+      <c r="I581" s="14">
+        <v>6.42</v>
+      </c>
+      <c r="J581" s="14">
+        <v>6.69</v>
+      </c>
+      <c r="K581" s="14">
+        <v>7.51</v>
+      </c>
+    </row>
+    <row r="582" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A582" s="13">
+        <v>46043</v>
+      </c>
+      <c r="B582" s="14">
+        <v>6.73</v>
+      </c>
+      <c r="C582" s="14">
+        <v>6.52</v>
+      </c>
+      <c r="D582" s="14">
+        <v>6.37</v>
+      </c>
+      <c r="E582" s="14">
+        <v>6.24</v>
+      </c>
+      <c r="F582" s="15">
+        <v>6.4649591326100264</v>
+      </c>
+      <c r="G582" s="14">
+        <v>6.23</v>
+      </c>
+      <c r="H582" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="I582" s="14">
+        <v>6.37</v>
+      </c>
+      <c r="J582" s="14">
+        <v>6.64</v>
+      </c>
+      <c r="K582" s="14">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="583" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A583" s="13">
+        <v>46044</v>
+      </c>
+      <c r="B583" s="14">
+        <v>6.73</v>
+      </c>
+      <c r="C583" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="D583" s="14">
+        <v>6.37</v>
+      </c>
+      <c r="E583" s="14">
+        <v>6.24</v>
+      </c>
+      <c r="F583" s="15">
+        <v>6.4599597173496726</v>
+      </c>
+      <c r="G583" s="14">
+        <v>6.22</v>
+      </c>
+      <c r="H583" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="I583" s="14">
+        <v>6.37</v>
+      </c>
+      <c r="J583" s="14">
+        <v>6.6</v>
+      </c>
+      <c r="K583" s="14">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="584" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A584" s="13">
+        <v>46045</v>
+      </c>
+      <c r="B584" s="14">
+        <v>6.73</v>
+      </c>
+      <c r="C584" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="D584" s="14">
+        <v>6.36</v>
+      </c>
+      <c r="E584" s="14">
+        <v>6.22</v>
+      </c>
+      <c r="F584" s="15">
+        <v>6.4524563719912109</v>
+      </c>
+      <c r="G584" s="14">
+        <v>6.19</v>
+      </c>
+      <c r="H584" s="14">
+        <v>6.32</v>
+      </c>
+      <c r="I584" s="14">
+        <v>6.35</v>
+      </c>
+      <c r="J584" s="14">
+        <v>6.59</v>
+      </c>
+      <c r="K584" s="14">
+        <v>7.38</v>
+      </c>
+    </row>
+    <row r="585" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A585" s="13">
+        <v>46048</v>
+      </c>
+      <c r="B585" s="14">
+        <v>6.72</v>
+      </c>
+      <c r="C585" s="14">
+        <v>6.49</v>
+      </c>
+      <c r="D585" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="E585" s="14">
+        <v>6.22</v>
+      </c>
+      <c r="F585" s="15">
+        <v>6.4324542804513385</v>
+      </c>
+      <c r="G585" s="14">
+        <v>6.19</v>
+      </c>
+      <c r="H585" s="14">
+        <v>6.31</v>
+      </c>
+      <c r="I585" s="14">
+        <v>6.33</v>
+      </c>
+      <c r="J585" s="14">
+        <v>6.57</v>
+      </c>
+      <c r="K585" s="14">
+        <v>7.36</v>
+      </c>
+    </row>
+    <row r="586" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A586" s="13">
+        <v>46049</v>
+      </c>
+      <c r="B586" s="14">
+        <v>6.71</v>
+      </c>
+      <c r="C586" s="14">
+        <v>6.49</v>
+      </c>
+      <c r="D586" s="14">
+        <v>6.29</v>
+      </c>
+      <c r="E586" s="14">
+        <v>6.2</v>
+      </c>
+      <c r="F586" s="15">
+        <v>6.4224525563239432</v>
+      </c>
+      <c r="G586" s="14">
+        <v>6.18</v>
+      </c>
+      <c r="H586" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="I586" s="14">
+        <v>6.33</v>
+      </c>
+      <c r="J586" s="14">
+        <v>6.57</v>
+      </c>
+      <c r="K586" s="14">
+        <v>7.36</v>
+      </c>
+    </row>
+    <row r="587" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A587" s="13">
+        <v>46050</v>
+      </c>
+      <c r="B587" s="14">
+        <v>6.7</v>
+      </c>
+      <c r="C587" s="14">
+        <v>6.48</v>
+      </c>
+      <c r="D587" s="14">
+        <v>6.26</v>
+      </c>
+      <c r="E587" s="14">
+        <v>6.16</v>
+      </c>
+      <c r="F587" s="15">
+        <v>6.3999466098451308</v>
+      </c>
+      <c r="G587" s="14">
+        <v>6.14</v>
+      </c>
+      <c r="H587" s="14">
+        <v>6.27</v>
+      </c>
+      <c r="I587" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="J587" s="14">
+        <v>6.55</v>
+      </c>
+      <c r="K587" s="14">
+        <v>7.33</v>
+      </c>
+    </row>
+    <row r="588" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A588" s="13">
+        <v>46051</v>
+      </c>
+      <c r="B588" s="14">
+        <v>6.7</v>
+      </c>
+      <c r="C588" s="14">
+        <v>6.56</v>
+      </c>
+      <c r="D588" s="14">
+        <v>6.33</v>
+      </c>
+      <c r="E588" s="14">
+        <v>6.22</v>
+      </c>
+      <c r="F588" s="15">
+        <v>6.4524563689058567</v>
+      </c>
+      <c r="G588" s="14">
+        <v>6.16</v>
+      </c>
+      <c r="H588" s="14">
+        <v>6.35</v>
+      </c>
+      <c r="I588" s="14">
+        <v>6.35</v>
+      </c>
+      <c r="J588" s="14">
+        <v>6.6</v>
+      </c>
+      <c r="K588" s="14">
+        <v>7.36</v>
+      </c>
+    </row>
+    <row r="589" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A589" s="13">
+        <v>46052</v>
+      </c>
+      <c r="B589" s="14">
+        <v>6.71</v>
+      </c>
+      <c r="C589" s="14">
+        <v>6.55</v>
+      </c>
+      <c r="D589" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="E589" s="14">
+        <v>6.24</v>
+      </c>
+      <c r="F589" s="15">
+        <v>6.4599589770554466</v>
+      </c>
+      <c r="G589" s="14">
+        <v>6.22</v>
+      </c>
+      <c r="H589" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="I589" s="14">
+        <v>6.36</v>
+      </c>
+      <c r="J589" s="14">
+        <v>6.6</v>
+      </c>
+      <c r="K589" s="14">
+        <v>7.34</v>
+      </c>
+    </row>
+    <row r="590" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A590" s="13">
+        <v>46055</v>
+      </c>
+      <c r="B590" s="14">
+        <v>6.71</v>
+      </c>
+      <c r="C590" s="14">
+        <v>6.54</v>
+      </c>
+      <c r="D590" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="E590" s="14">
+        <v>6.23</v>
+      </c>
+      <c r="F590" s="15">
+        <v>6.454958146354528</v>
+      </c>
+      <c r="G590" s="14">
+        <v>6.18</v>
+      </c>
+      <c r="H590" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="I590" s="14">
+        <v>6.35</v>
+      </c>
+      <c r="J590" s="14">
+        <v>6.59</v>
+      </c>
+      <c r="K590" s="14">
+        <v>7.33</v>
+      </c>
+    </row>
+    <row r="591" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A591" s="13">
+        <v>46056</v>
+      </c>
+      <c r="B591" s="14">
+        <v>6.71</v>
+      </c>
+      <c r="C591" s="14">
+        <v>6.56</v>
+      </c>
+      <c r="D591" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="E591" s="14">
+        <v>6.24</v>
+      </c>
+      <c r="F591" s="15">
+        <v>6.4624584003112773</v>
+      </c>
+      <c r="G591" s="14">
+        <v>6.2</v>
+      </c>
+      <c r="H591" s="14">
+        <v>6.33</v>
+      </c>
+      <c r="I591" s="14">
+        <v>6.35</v>
+      </c>
+      <c r="J591" s="14">
+        <v>6.59</v>
+      </c>
+      <c r="K591" s="14">
+        <v>7.31</v>
+      </c>
+    </row>
+    <row r="592" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A592" s="13">
+        <v>46057</v>
+      </c>
+      <c r="B592" s="14">
+        <v>6.71</v>
+      </c>
+      <c r="C592" s="14">
+        <v>6.53</v>
+      </c>
+      <c r="D592" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="E592" s="14">
+        <v>6.22</v>
+      </c>
+      <c r="F592" s="15">
+        <v>6.4499572541250494</v>
+      </c>
+      <c r="G592" s="14">
+        <v>6.18</v>
+      </c>
+      <c r="H592" s="14">
+        <v>6.32</v>
+      </c>
+      <c r="I592" s="14">
+        <v>6.35</v>
+      </c>
+      <c r="J592" s="14">
+        <v>6.59</v>
+      </c>
+      <c r="K592" s="14">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="593" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A593" s="13">
+        <v>46058</v>
+      </c>
+      <c r="B593" s="14">
+        <v>6.68</v>
+      </c>
+      <c r="C593" s="14">
+        <v>6.52</v>
+      </c>
+      <c r="D593" s="14">
+        <v>6.33</v>
+      </c>
+      <c r="E593" s="14">
+        <v>6.23</v>
+      </c>
+      <c r="F593" s="15">
+        <v>6.4399630345592485</v>
+      </c>
+      <c r="G593" s="14">
+        <v>6.2</v>
+      </c>
+      <c r="H593" s="14">
+        <v>6.32</v>
+      </c>
+      <c r="I593" s="14">
+        <v>6.35</v>
+      </c>
+      <c r="J593" s="14">
+        <v>6.59</v>
+      </c>
+      <c r="K593" s="14">
+        <v>7.33</v>
+      </c>
+    </row>
+    <row r="594" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A594" s="13">
+        <v>46059</v>
+      </c>
+      <c r="B594" s="14">
+        <v>6.68</v>
+      </c>
+      <c r="C594" s="14">
+        <v>6.53</v>
+      </c>
+      <c r="D594" s="14">
+        <v>6.32</v>
+      </c>
+      <c r="E594" s="14">
+        <v>6.23</v>
+      </c>
+      <c r="F594" s="15">
+        <v>6.4399618042745743</v>
+      </c>
+      <c r="G594" s="14">
+        <v>6.2</v>
+      </c>
+      <c r="H594" s="14">
+        <v>6.31</v>
+      </c>
+      <c r="I594" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="J594" s="14">
+        <v>6.58</v>
+      </c>
+      <c r="K594" s="14">
+        <v>7.32</v>
+      </c>
+    </row>
+    <row r="595" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A595" s="13">
+        <v>46062</v>
+      </c>
+      <c r="B595" s="14">
+        <v>6.67</v>
+      </c>
+      <c r="C595" s="14">
+        <v>6.52</v>
+      </c>
+      <c r="D595" s="14">
+        <v>6.31</v>
+      </c>
+      <c r="E595" s="14">
+        <v>6.21</v>
+      </c>
+      <c r="F595" s="15">
+        <v>6.4274604880758979</v>
+      </c>
+      <c r="G595" s="14">
+        <v>6.18</v>
+      </c>
+      <c r="H595" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="I595" s="14">
+        <v>6.32</v>
+      </c>
+      <c r="J595" s="14">
+        <v>6.55</v>
+      </c>
+      <c r="K595" s="14">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="596" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A596" s="13">
+        <v>46063</v>
+      </c>
+      <c r="B596" s="14">
+        <v>6.67</v>
+      </c>
+      <c r="C596" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="D596" s="14">
+        <v>6.29</v>
+      </c>
+      <c r="E596" s="14">
+        <v>6.2</v>
+      </c>
+      <c r="F596" s="15">
+        <v>6.4149587578851808</v>
+      </c>
+      <c r="G596" s="14">
+        <v>6.16</v>
+      </c>
+      <c r="H596" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="I596" s="14">
+        <v>6.31</v>
+      </c>
+      <c r="J596" s="14">
+        <v>6.53</v>
+      </c>
+      <c r="K596" s="14">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="597" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A597" s="13">
+        <v>46064</v>
+      </c>
+      <c r="B597" s="14">
+        <v>6.67</v>
+      </c>
+      <c r="C597" s="14">
+        <v>6.51</v>
+      </c>
+      <c r="D597" s="14">
+        <v>6.31</v>
+      </c>
+      <c r="E597" s="14">
+        <v>6.21</v>
+      </c>
+      <c r="F597" s="15">
+        <v>6.4249610341149399</v>
+      </c>
+      <c r="G597" s="14">
+        <v>6.18</v>
+      </c>
+      <c r="H597" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="I597" s="14">
+        <v>6.32</v>
+      </c>
+      <c r="J597" s="14">
+        <v>6.54</v>
+      </c>
+      <c r="K597" s="14">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="598" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A598" s="13">
+        <v>46065</v>
+      </c>
+      <c r="B598" s="14">
+        <v>6.67</v>
+      </c>
+      <c r="C598" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="D598" s="14">
+        <v>6.2949999999999999</v>
+      </c>
+      <c r="E598" s="14">
+        <v>6.1899999999999995</v>
+      </c>
+      <c r="F598" s="15">
+        <v>6.4137077154398092</v>
+      </c>
+      <c r="G598" s="14">
+        <v>6.15</v>
+      </c>
+      <c r="H598" s="14">
+        <v>6.2850000000000001</v>
+      </c>
+      <c r="I598" s="14">
+        <v>6.3000000000000007</v>
+      </c>
+      <c r="J598" s="14">
+        <v>6.52</v>
+      </c>
+      <c r="K598" s="14">
+        <v>7.2249999999999996</v>
+      </c>
+    </row>
+    <row r="599" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A599" s="13">
+        <v>46066</v>
+      </c>
+      <c r="B599" s="14">
+        <v>6.67</v>
+      </c>
+      <c r="C599" s="14">
+        <v>6.49</v>
+      </c>
+      <c r="D599" s="14">
+        <v>6.28</v>
+      </c>
+      <c r="E599" s="14">
+        <v>6.17</v>
+      </c>
+      <c r="F599" s="15">
+        <v>6.4024543967646785</v>
+      </c>
+      <c r="G599" s="14">
+        <v>6.12</v>
+      </c>
+      <c r="H599" s="14">
+        <v>6.27</v>
+      </c>
+      <c r="I599" s="14">
+        <v>6.28</v>
+      </c>
+      <c r="J599" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="K599" s="14">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="600" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A600" s="13">
+        <v>46069</v>
+      </c>
+      <c r="B600" s="14">
+        <v>6.67</v>
+      </c>
+      <c r="C600" s="14">
+        <v>6.49</v>
+      </c>
+      <c r="D600" s="14">
+        <v>6.27</v>
+      </c>
+      <c r="E600" s="14">
+        <v>6.14</v>
+      </c>
+      <c r="F600" s="15">
+        <v>6.3924491661787819</v>
+      </c>
+      <c r="G600" s="14">
+        <v>6.08</v>
+      </c>
+      <c r="H600" s="14">
+        <v>6.274</v>
+      </c>
+      <c r="I600" s="14">
+        <v>6.25</v>
+      </c>
+      <c r="J600" s="14">
+        <v>6.46</v>
+      </c>
+      <c r="K600" s="14">
+        <v>7.16</v>
+      </c>
+    </row>
+    <row r="601" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A601" s="13">
+        <v>46070</v>
+      </c>
+      <c r="B601" s="14">
+        <v>6.66</v>
+      </c>
+      <c r="C601" s="14">
+        <v>6.49</v>
+      </c>
+      <c r="D601" s="14">
+        <v>6.28</v>
+      </c>
+      <c r="E601" s="14">
+        <v>6.14</v>
+      </c>
+      <c r="F601" s="15">
+        <v>6.3924515644226965</v>
+      </c>
+      <c r="G601" s="14">
+        <v>6.07</v>
+      </c>
+      <c r="H601" s="14">
+        <v>6.274</v>
+      </c>
+      <c r="I601" s="14">
+        <v>6.24</v>
+      </c>
+      <c r="J601" s="14">
+        <v>6.43</v>
+      </c>
+      <c r="K601" s="14">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="602" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A602" s="13">
+        <v>46071</v>
+      </c>
+      <c r="B602" s="14">
+        <v>6.6566666666666672</v>
+      </c>
+      <c r="C602" s="14">
+        <v>6.49</v>
+      </c>
+      <c r="D602" s="14">
+        <v>6.28</v>
+      </c>
+      <c r="E602" s="14">
+        <v>6.14</v>
+      </c>
+      <c r="F602" s="15">
+        <v>6.3924515644226965</v>
+      </c>
+      <c r="G602" s="14">
+        <v>6.07</v>
+      </c>
+      <c r="H602" s="14">
+        <v>6.274</v>
+      </c>
+      <c r="I602" s="14">
+        <v>6.24</v>
+      </c>
+      <c r="J602" s="14">
+        <v>6.43</v>
+      </c>
+      <c r="K602" s="14">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="603" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A603" s="13">
+        <v>46072</v>
+      </c>
+      <c r="B603" s="14">
+        <v>6.6533333333333342</v>
+      </c>
+      <c r="C603" s="14">
+        <v>6.49</v>
+      </c>
+      <c r="D603" s="14">
+        <v>6.28</v>
+      </c>
+      <c r="E603" s="14">
+        <v>6.14</v>
+      </c>
+      <c r="F603" s="15">
+        <v>6.3924515644226965</v>
+      </c>
+      <c r="G603" s="14">
+        <v>6.07</v>
+      </c>
+      <c r="H603" s="14">
+        <v>6.274</v>
+      </c>
+      <c r="I603" s="14">
+        <v>6.24</v>
+      </c>
+      <c r="J603" s="14">
+        <v>6.43</v>
+      </c>
+      <c r="K603" s="14">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="604" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A604" s="13">
+        <v>46073</v>
+      </c>
+      <c r="B604" s="14">
+        <v>6.65</v>
+      </c>
+      <c r="C604" s="14">
+        <v>6.53</v>
+      </c>
+      <c r="D604" s="14">
+        <v>6.37</v>
+      </c>
+      <c r="E604" s="14">
+        <v>6.2</v>
+      </c>
+      <c r="F604" s="15">
+        <v>6.4374647299856314</v>
+      </c>
+      <c r="G604" s="14">
+        <v>6.18</v>
+      </c>
+      <c r="H604" s="14">
+        <v>6.31</v>
+      </c>
+      <c r="I604" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="J604" s="14">
+        <v>6.55</v>
+      </c>
+      <c r="K604" s="14">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="605" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A605" s="13">
+        <v>46076</v>
+      </c>
+      <c r="B605" s="14">
+        <v>6.65</v>
+      </c>
+      <c r="C605" s="14">
+        <v>6.51</v>
+      </c>
+      <c r="D605" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="E605" s="14">
+        <v>6.17</v>
+      </c>
+      <c r="F605" s="15">
+        <v>6.4174600537831417</v>
+      </c>
+      <c r="G605" s="14">
+        <v>6.15</v>
+      </c>
+      <c r="H605" s="14">
+        <v>6.29</v>
+      </c>
+      <c r="I605" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="J605" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="K605" s="14">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="606" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A606" s="13">
+        <v>46077</v>
+      </c>
+      <c r="B606" s="14">
+        <v>6.64</v>
+      </c>
+      <c r="C606" s="14">
+        <v>6.51</v>
+      </c>
+      <c r="D606" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="E606" s="14">
+        <v>6.18</v>
+      </c>
+      <c r="F606" s="15">
+        <v>6.4174629450062248</v>
+      </c>
+      <c r="G606" s="14">
+        <v>6.16</v>
+      </c>
+      <c r="H606" s="14">
+        <v>6.29</v>
+      </c>
+      <c r="I606" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="J606" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="K606" s="14">
+        <v>7.18</v>
+      </c>
+    </row>
+    <row r="607" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A607" s="13">
+        <v>46078</v>
+      </c>
+      <c r="B607" s="14">
+        <v>6.63</v>
+      </c>
+      <c r="C607" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="D607" s="14">
+        <v>6.33</v>
+      </c>
+      <c r="E607" s="14">
+        <v>6.17</v>
+      </c>
+      <c r="F607" s="15">
+        <v>6.4074629440944442</v>
+      </c>
+      <c r="G607" s="14">
+        <v>6.16</v>
+      </c>
+      <c r="H607" s="14">
+        <v>6.29</v>
+      </c>
+      <c r="I607" s="14">
+        <v>6.29</v>
+      </c>
+      <c r="J607" s="14">
+        <v>6.48</v>
+      </c>
+      <c r="K607" s="14">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="608" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A608" s="13">
+        <v>46079</v>
+      </c>
+      <c r="B608" s="14">
+        <v>6.63</v>
+      </c>
+      <c r="C608" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="D608" s="14">
+        <v>6.36</v>
+      </c>
+      <c r="E608" s="14">
+        <v>6.22</v>
+      </c>
+      <c r="F608" s="15">
+        <v>6.4274711277162666</v>
+      </c>
+      <c r="G608" s="14">
+        <v>6.21</v>
+      </c>
+      <c r="H608" s="14">
+        <v>6.32</v>
+      </c>
+      <c r="I608" s="14">
+        <v>6.33</v>
+      </c>
+      <c r="J608" s="14">
+        <v>6.55</v>
+      </c>
+      <c r="K608" s="14">
+        <v>7.18</v>
+      </c>
+    </row>
+    <row r="609" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A609" s="13">
+        <v>46080</v>
+      </c>
+      <c r="B609" s="14">
+        <v>6.63</v>
+      </c>
+      <c r="C609" s="14">
+        <v>6.49</v>
+      </c>
+      <c r="D609" s="14">
+        <v>6.38</v>
+      </c>
+      <c r="E609" s="14">
+        <v>6.24</v>
+      </c>
+      <c r="F609" s="15">
+        <v>6.4349747499580445</v>
+      </c>
+      <c r="G609" s="14">
+        <v>6.24</v>
+      </c>
+      <c r="H609" s="14">
+        <v>6.34</v>
+      </c>
+      <c r="I609" s="14">
+        <v>6.36</v>
+      </c>
+      <c r="J609" s="14">
+        <v>6.56</v>
+      </c>
+      <c r="K609" s="14">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="610" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A610" s="13">
+        <v>46083</v>
+      </c>
+      <c r="B610" s="14">
+        <v>6.63</v>
+      </c>
+      <c r="C610" s="14">
+        <v>6.58</v>
+      </c>
+      <c r="D610" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="E610" s="14">
+        <v>6.38</v>
+      </c>
+      <c r="F610" s="15">
+        <v>6.5224890296920357</v>
+      </c>
+      <c r="G610" s="14">
+        <v>6.37</v>
+      </c>
+      <c r="H610" s="14">
+        <v>6.45</v>
+      </c>
+      <c r="I610" s="14">
+        <v>6.48</v>
+      </c>
+      <c r="J610" s="14">
+        <v>6.69</v>
+      </c>
+      <c r="K610" s="14">
+        <v>7.37</v>
+      </c>
+    </row>
+    <row r="611" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A611" s="13">
+        <v>46084</v>
+      </c>
+      <c r="B611" s="14">
+        <v>6.63</v>
+      </c>
+      <c r="C611" s="14">
+        <v>6.64</v>
+      </c>
+      <c r="D611" s="14">
+        <v>6.6</v>
+      </c>
+      <c r="E611" s="14">
+        <v>6.51</v>
+      </c>
+      <c r="F611" s="15">
+        <v>6.5949967717300773</v>
+      </c>
+      <c r="G611" s="14">
+        <v>6.52</v>
+      </c>
+      <c r="H611" s="14">
+        <v>6.54</v>
+      </c>
+      <c r="I611" s="14">
+        <v>6.61</v>
+      </c>
+      <c r="J611" s="14">
+        <v>6.86</v>
+      </c>
+      <c r="K611" s="14">
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="612" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A612" s="13">
+        <v>46085</v>
+      </c>
+      <c r="B612" s="14">
+        <v>6.63</v>
+      </c>
+      <c r="C612" s="14">
+        <v>6.59</v>
+      </c>
+      <c r="D612" s="14">
+        <v>6.53</v>
+      </c>
+      <c r="E612" s="14">
+        <v>6.43</v>
+      </c>
+      <c r="F612" s="15">
+        <v>6.5449930200397688</v>
+      </c>
+      <c r="G612" s="14">
+        <v>6.42</v>
+      </c>
+      <c r="H612" s="14">
+        <v>6.48</v>
+      </c>
+      <c r="I612" s="14">
+        <v>6.52</v>
+      </c>
+      <c r="J612" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="K612" s="14">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="613" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A613" s="13">
+        <v>46086</v>
+      </c>
+      <c r="B613" s="14">
+        <v>6.63</v>
+      </c>
+      <c r="C613" s="14">
+        <v>6.64</v>
+      </c>
+      <c r="D613" s="14">
+        <v>6.6</v>
+      </c>
+      <c r="E613" s="14">
+        <v>6.53</v>
+      </c>
+      <c r="F613" s="15">
+        <v>6.5999977249098229</v>
+      </c>
+      <c r="G613" s="14">
+        <v>6.52</v>
+      </c>
+      <c r="H613" s="14">
+        <v>6.55</v>
+      </c>
+      <c r="I613" s="14">
+        <v>6.6</v>
+      </c>
+      <c r="J613" s="14">
+        <v>6.82</v>
+      </c>
+      <c r="K613" s="14">
+        <v>7.53</v>
+      </c>
+    </row>
+    <row r="614" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A614" s="13">
+        <v>46087</v>
+      </c>
+      <c r="B614" s="14">
+        <v>6.65</v>
+      </c>
+      <c r="C614" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="D614" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="E614" s="14">
+        <v>6.76</v>
+      </c>
+      <c r="F614" s="15">
+        <v>6.7274975180957597</v>
+      </c>
+      <c r="G614" s="14">
+        <v>6.77</v>
+      </c>
+      <c r="H614" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="I614" s="14">
+        <v>6.82</v>
+      </c>
+      <c r="J614" s="14">
+        <v>7.05</v>
+      </c>
+      <c r="K614" s="14">
+        <v>7.77</v>
+      </c>
+    </row>
+    <row r="615" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A615" s="13">
+        <v>46090</v>
+      </c>
+      <c r="B615" s="14">
+        <v>6.67</v>
+      </c>
+      <c r="C615" s="14">
+        <v>6.81</v>
+      </c>
+      <c r="D615" s="14">
+        <v>6.84</v>
+      </c>
+      <c r="E615" s="14">
+        <v>6.85</v>
+      </c>
+      <c r="F615" s="15">
+        <v>6.7924935847154089</v>
+      </c>
+      <c r="G615" s="14">
+        <v>6.88</v>
+      </c>
+      <c r="H615" s="14">
+        <v>6.85</v>
+      </c>
+      <c r="I615" s="14">
+        <v>6.9</v>
+      </c>
+      <c r="J615" s="14">
+        <v>7.12</v>
+      </c>
+      <c r="K615" s="14">
+        <v>7.82</v>
+      </c>
+    </row>
+    <row r="616" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A616" s="13">
+        <v>46091</v>
+      </c>
+      <c r="B616" s="14">
+        <v>6.68</v>
+      </c>
+      <c r="C616" s="14">
+        <v>6.74</v>
+      </c>
+      <c r="D616" s="14">
+        <v>6.74</v>
+      </c>
+      <c r="E616" s="14">
+        <v>6.74</v>
+      </c>
+      <c r="F616" s="15">
+        <v>6.7249991701602063</v>
+      </c>
+      <c r="G616" s="14">
+        <v>6.71</v>
+      </c>
+      <c r="H616" s="14">
+        <v>6.73</v>
+      </c>
+      <c r="I616" s="14">
+        <v>6.76</v>
+      </c>
+      <c r="J616" s="14">
+        <v>6.96</v>
+      </c>
+      <c r="K616" s="14">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="617" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A617" s="13">
+        <v>46092</v>
+      </c>
+      <c r="B617" s="14">
+        <v>6.68</v>
+      </c>
+      <c r="C617" s="14">
+        <v>6.83</v>
+      </c>
+      <c r="D617" s="14">
+        <v>6.89</v>
+      </c>
+      <c r="E617" s="14">
+        <v>6.92</v>
+      </c>
+      <c r="F617" s="15">
+        <v>6.8299894907014824</v>
+      </c>
+      <c r="G617" s="14">
+        <v>6.91</v>
+      </c>
+      <c r="H617" s="14">
+        <v>6.87</v>
+      </c>
+      <c r="I617" s="14">
+        <v>6.92</v>
+      </c>
+      <c r="J617" s="14">
+        <v>7.12</v>
+      </c>
+      <c r="K617" s="14">
+        <v>7.77</v>
+      </c>
+    </row>
+    <row r="618" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A618" s="13">
+        <v>46093</v>
+      </c>
+      <c r="B618" s="14">
+        <v>6.68</v>
+      </c>
+      <c r="C618" s="14">
+        <v>6.91</v>
+      </c>
+      <c r="D618" s="14">
+        <v>7.12</v>
+      </c>
+      <c r="E618" s="14">
+        <v>7.26</v>
+      </c>
+      <c r="F618" s="15">
+        <v>6.9924409414206856</v>
+      </c>
+      <c r="G618" s="14">
+        <v>7.29</v>
+      </c>
+      <c r="H618" s="14">
+        <v>7.13</v>
+      </c>
+      <c r="I618" s="14">
+        <v>7.22</v>
+      </c>
+      <c r="J618" s="14">
+        <v>7.43</v>
+      </c>
+      <c r="K618" s="14">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="619" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A619" s="13">
+        <v>46094</v>
+      </c>
+      <c r="B619" s="14">
+        <v>6.7</v>
+      </c>
+      <c r="C619" s="14">
+        <v>6.93</v>
+      </c>
+      <c r="D619" s="14">
+        <v>7.2</v>
+      </c>
+      <c r="E619" s="14">
+        <v>7.39</v>
+      </c>
+      <c r="F619" s="15">
+        <v>7.0549155796007845</v>
+      </c>
+      <c r="G619" s="14">
+        <v>7.45</v>
+      </c>
+      <c r="H619" s="14">
+        <v>7.23</v>
+      </c>
+      <c r="I619" s="14">
+        <v>7.34</v>
+      </c>
+      <c r="J619" s="14">
+        <v>7.59</v>
+      </c>
+      <c r="K619" s="14">
+        <v>8.2200000000000006</v>
+      </c>
+    </row>
+    <row r="620" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A620" s="13">
+        <v>46097</v>
+      </c>
+      <c r="B620" s="14">
+        <v>6.7249999999999996</v>
+      </c>
+      <c r="C620" s="14">
+        <v>6.91</v>
+      </c>
+      <c r="D620" s="14">
+        <v>7.13</v>
+      </c>
+      <c r="E620" s="14">
+        <v>7.2750000000000004</v>
+      </c>
+      <c r="F620" s="15">
+        <v>7.0099426006213772</v>
+      </c>
+      <c r="G620" s="14">
+        <v>7.3250000000000002</v>
+      </c>
+      <c r="H620" s="14">
+        <v>7.15</v>
+      </c>
+      <c r="I620" s="14">
+        <v>7.2450000000000001</v>
+      </c>
+      <c r="J620" s="14">
+        <v>7.48</v>
+      </c>
+      <c r="K620" s="14">
+        <v>8.1150000000000002</v>
+      </c>
+    </row>
+    <row r="621" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A621" s="13">
+        <v>46098</v>
+      </c>
+      <c r="B621" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C621" s="14">
+        <v>6.89</v>
+      </c>
+      <c r="D621" s="14">
+        <v>7.06</v>
+      </c>
+      <c r="E621" s="14">
+        <v>7.16</v>
+      </c>
+      <c r="F621" s="15">
+        <v>6.9649696216419699</v>
+      </c>
+      <c r="G621" s="14">
+        <v>7.2</v>
+      </c>
+      <c r="H621" s="14">
+        <v>7.07</v>
+      </c>
+      <c r="I621" s="14">
+        <v>7.15</v>
+      </c>
+      <c r="J621" s="14">
+        <v>7.37</v>
+      </c>
+      <c r="K621" s="14">
+        <v>8.01</v>
+      </c>
+    </row>
+    <row r="622" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A622" s="13">
+        <v>46099</v>
+      </c>
+      <c r="B622" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C622" s="14">
+        <v>6.95</v>
+      </c>
+      <c r="D622" s="14">
+        <v>7.2</v>
+      </c>
+      <c r="E622" s="14">
+        <v>7.36</v>
+      </c>
+      <c r="F622" s="15">
+        <v>7.0649331471503984</v>
+      </c>
+      <c r="G622" s="14">
+        <v>7.41</v>
+      </c>
+      <c r="H622" s="14">
+        <v>7.23</v>
+      </c>
+      <c r="I622" s="14">
+        <v>7.33</v>
+      </c>
+      <c r="J622" s="14">
+        <v>7.57</v>
+      </c>
+      <c r="K622" s="14">
+        <v>8.2200000000000006</v>
+      </c>
+    </row>
+    <row r="623" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A623" s="13">
+        <v>46100</v>
+      </c>
+      <c r="B623" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C623" s="14">
+        <v>7.09</v>
+      </c>
+      <c r="D623" s="14">
+        <v>7.36</v>
+      </c>
+      <c r="E623" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="F623" s="15">
+        <v>7.1748993798069094</v>
+      </c>
+      <c r="G623" s="14">
+        <v>7.55</v>
+      </c>
+      <c r="H623" s="14">
+        <v>7.36</v>
+      </c>
+      <c r="I623" s="14">
+        <v>7.46</v>
+      </c>
+      <c r="J623" s="14">
+        <v>7.69</v>
+      </c>
+      <c r="K623" s="14">
+        <v>8.31</v>
+      </c>
+    </row>
+    <row r="624" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A624" s="13">
+        <v>46101</v>
+      </c>
+      <c r="B624" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C624" s="14">
+        <v>7.17</v>
+      </c>
+      <c r="D624" s="14">
+        <v>7.47</v>
+      </c>
+      <c r="E624" s="14">
+        <v>7.65</v>
+      </c>
+      <c r="F624" s="15">
+        <v>7.2598574294451268</v>
+      </c>
+      <c r="G624" s="14">
+        <v>7.67</v>
+      </c>
+      <c r="H624" s="14">
+        <v>7.45</v>
+      </c>
+      <c r="I624" s="14">
+        <v>7.57</v>
+      </c>
+      <c r="J624" s="14">
+        <v>7.8</v>
+      </c>
+      <c r="K624" s="14">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="625" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A625" s="13">
+        <v>46104</v>
+      </c>
+      <c r="B625" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C625" s="14">
+        <v>7.11</v>
+      </c>
+      <c r="D625" s="14">
+        <v>7.37</v>
+      </c>
+      <c r="E625" s="14">
+        <v>7.51</v>
+      </c>
+      <c r="F625" s="15">
+        <v>7.1848972306842285</v>
+      </c>
+      <c r="G625" s="14">
+        <v>7.49</v>
+      </c>
+      <c r="H625" s="14">
+        <v>7.3</v>
+      </c>
+      <c r="I625" s="14">
+        <v>7.39</v>
+      </c>
+      <c r="J625" s="14">
+        <v>7.59</v>
+      </c>
+      <c r="K625" s="14">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="626" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A626" s="13">
+        <v>46105</v>
+      </c>
+      <c r="B626" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C626" s="14">
+        <v>7.15</v>
+      </c>
+      <c r="D626" s="14">
+        <v>7.52</v>
+      </c>
+      <c r="E626" s="14">
+        <v>7.61</v>
+      </c>
+      <c r="F626" s="15">
+        <v>7.2573580781591041</v>
+      </c>
+      <c r="G626" s="14">
+        <v>7.6</v>
+      </c>
+      <c r="H626" s="14">
+        <v>7.42</v>
+      </c>
+      <c r="I626" s="14">
+        <v>7.52</v>
+      </c>
+      <c r="J626" s="14">
+        <v>7.72</v>
+      </c>
+      <c r="K626" s="14">
+        <v>8.31</v>
+      </c>
+    </row>
+    <row r="627" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A627" s="13">
+        <v>46106</v>
+      </c>
+      <c r="B627" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C627" s="14">
+        <v>7.13</v>
+      </c>
+      <c r="D627" s="14">
+        <v>7.49</v>
+      </c>
+      <c r="E627" s="14">
+        <v>7.55</v>
+      </c>
+      <c r="F627" s="15">
+        <v>7.229873996141567</v>
+      </c>
+      <c r="G627" s="14">
+        <v>7.48</v>
+      </c>
+      <c r="H627" s="14">
+        <v>7.36</v>
+      </c>
+      <c r="I627" s="14">
+        <v>7.43</v>
+      </c>
+      <c r="J627" s="14">
+        <v>7.64</v>
+      </c>
+      <c r="K627" s="14">
+        <v>8.2100000000000009</v>
+      </c>
+    </row>
+    <row r="628" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A628" s="13">
+        <v>46107</v>
+      </c>
+      <c r="B628" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C628" s="14">
+        <v>7.11</v>
+      </c>
+      <c r="D628" s="14">
+        <v>7.48</v>
+      </c>
+      <c r="E628" s="14">
+        <v>7.52</v>
+      </c>
+      <c r="F628" s="15">
+        <v>7.2148801033517174</v>
+      </c>
+      <c r="G628" s="14">
+        <v>7.26</v>
+      </c>
+      <c r="H628" s="14">
+        <v>7.32</v>
+      </c>
+      <c r="I628" s="14">
+        <v>7.43</v>
+      </c>
+      <c r="J628" s="14">
+        <v>7.66</v>
+      </c>
+      <c r="K628" s="14">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="629" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A629" s="13">
+        <v>46108</v>
+      </c>
+      <c r="B629" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C629" s="14">
+        <v>7.18</v>
+      </c>
+      <c r="D629" s="14">
+        <v>7.57</v>
+      </c>
+      <c r="E629" s="14">
+        <v>7.63</v>
+      </c>
+      <c r="F629" s="15">
+        <v>7.2823472753715812</v>
+      </c>
+      <c r="G629" s="14">
+        <v>7.6</v>
+      </c>
+      <c r="H629" s="14">
+        <v>7.46</v>
+      </c>
+      <c r="I629" s="14">
+        <v>7.56</v>
+      </c>
+      <c r="J629" s="14">
+        <v>7.8</v>
+      </c>
+      <c r="K629" s="14">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="630" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A630" s="13">
+        <v>46111</v>
+      </c>
+      <c r="B630" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C630" s="14">
+        <v>7.17</v>
+      </c>
+      <c r="D630" s="14">
+        <v>7.58</v>
+      </c>
+      <c r="E630" s="14">
+        <v>7.65</v>
+      </c>
+      <c r="F630" s="15">
+        <v>7.2873404649270945</v>
+      </c>
+      <c r="G630" s="14">
+        <v>7.62</v>
+      </c>
+      <c r="H630" s="14">
+        <v>7.45</v>
+      </c>
+      <c r="I630" s="14">
+        <v>7.55</v>
+      </c>
+      <c r="J630" s="14">
+        <v>7.81</v>
+      </c>
+      <c r="K630" s="14">
+        <v>8.4600000000000009</v>
+      </c>
+    </row>
+    <row r="631" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A631" s="13">
+        <v>46112</v>
+      </c>
+      <c r="B631" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C631" s="14">
+        <v>7.12</v>
+      </c>
+      <c r="D631" s="14">
+        <v>7.47</v>
+      </c>
+      <c r="E631" s="14">
+        <v>7.53</v>
+      </c>
+      <c r="F631" s="15">
+        <v>7.2173804178348178</v>
+      </c>
+      <c r="G631" s="14">
+        <v>7.49</v>
+      </c>
+      <c r="H631" s="14">
+        <v>7.35</v>
+      </c>
+      <c r="I631" s="14">
+        <v>7.44</v>
+      </c>
+      <c r="J631" s="14">
+        <v>7.69</v>
+      </c>
+      <c r="K631" s="14">
+        <v>8.35</v>
       </c>
     </row>
   </sheetData>

--- a/JIBAR_FRA_SWAPS.xlsx
+++ b/JIBAR_FRA_SWAPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pv01-my.sharepoint.com/personal/gordon_pv01_co_za/Documents/Projects/zaronia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{1B814A78-7EB1-4270-BC93-EA09DFB8DBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19F14F68-F54A-4BAF-B533-D096B88B7841}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{1B814A78-7EB1-4270-BC93-EA09DFB8DBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84E0FE3C-9720-408D-8776-E62DB36532C5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{34753434-5FEB-48FC-8487-529A3B1ADE64}"/>
   </bookViews>
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ACB4107-8137-49C4-AFE3-6FF31C87A0A4}">
-  <dimension ref="A1:K631"/>
+  <dimension ref="A1:K638"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
@@ -22647,6 +22647,258 @@
         <v>8.35</v>
       </c>
     </row>
+    <row r="632" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A632" s="13">
+        <f t="shared" ref="A632:A638" si="0">A631+1</f>
+        <v>46113</v>
+      </c>
+      <c r="B632" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C632" s="14">
+        <v>7.12</v>
+      </c>
+      <c r="D632" s="14">
+        <v>7.47</v>
+      </c>
+      <c r="E632" s="14">
+        <v>7.53</v>
+      </c>
+      <c r="F632" s="15">
+        <v>7.2173804178348178</v>
+      </c>
+      <c r="G632" s="14">
+        <v>7.49</v>
+      </c>
+      <c r="H632" s="14">
+        <v>7.35</v>
+      </c>
+      <c r="I632" s="14">
+        <v>7.44</v>
+      </c>
+      <c r="J632" s="14">
+        <v>7.69</v>
+      </c>
+      <c r="K632" s="14">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="633" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A633" s="13">
+        <f t="shared" si="0"/>
+        <v>46114</v>
+      </c>
+      <c r="B633" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C633" s="14">
+        <v>7.12</v>
+      </c>
+      <c r="D633" s="14">
+        <v>7.47</v>
+      </c>
+      <c r="E633" s="14">
+        <v>7.53</v>
+      </c>
+      <c r="F633" s="15">
+        <v>7.2173804178348178</v>
+      </c>
+      <c r="G633" s="14">
+        <v>7.49</v>
+      </c>
+      <c r="H633" s="14">
+        <v>7.35</v>
+      </c>
+      <c r="I633" s="14">
+        <v>7.44</v>
+      </c>
+      <c r="J633" s="14">
+        <v>7.69</v>
+      </c>
+      <c r="K633" s="14">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="634" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A634" s="13">
+        <f t="shared" si="0"/>
+        <v>46115</v>
+      </c>
+      <c r="B634" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C634" s="14">
+        <v>7.12</v>
+      </c>
+      <c r="D634" s="14">
+        <v>7.47</v>
+      </c>
+      <c r="E634" s="14">
+        <v>7.53</v>
+      </c>
+      <c r="F634" s="15">
+        <v>7.2173804178348178</v>
+      </c>
+      <c r="G634" s="14">
+        <v>7.49</v>
+      </c>
+      <c r="H634" s="14">
+        <v>7.35</v>
+      </c>
+      <c r="I634" s="14">
+        <v>7.44</v>
+      </c>
+      <c r="J634" s="14">
+        <v>7.69</v>
+      </c>
+      <c r="K634" s="14">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="635" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A635" s="13">
+        <f t="shared" si="0"/>
+        <v>46116</v>
+      </c>
+      <c r="B635" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C635" s="14">
+        <v>7.12</v>
+      </c>
+      <c r="D635" s="14">
+        <v>7.47</v>
+      </c>
+      <c r="E635" s="14">
+        <v>7.53</v>
+      </c>
+      <c r="F635" s="15">
+        <v>7.2173804178348178</v>
+      </c>
+      <c r="G635" s="14">
+        <v>7.49</v>
+      </c>
+      <c r="H635" s="14">
+        <v>7.35</v>
+      </c>
+      <c r="I635" s="14">
+        <v>7.44</v>
+      </c>
+      <c r="J635" s="14">
+        <v>7.69</v>
+      </c>
+      <c r="K635" s="14">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="636" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A636" s="13">
+        <f t="shared" si="0"/>
+        <v>46117</v>
+      </c>
+      <c r="B636" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C636" s="14">
+        <v>7.12</v>
+      </c>
+      <c r="D636" s="14">
+        <v>7.47</v>
+      </c>
+      <c r="E636" s="14">
+        <v>7.53</v>
+      </c>
+      <c r="F636" s="15">
+        <v>7.2173804178348178</v>
+      </c>
+      <c r="G636" s="14">
+        <v>7.49</v>
+      </c>
+      <c r="H636" s="14">
+        <v>7.35</v>
+      </c>
+      <c r="I636" s="14">
+        <v>7.44</v>
+      </c>
+      <c r="J636" s="14">
+        <v>7.69</v>
+      </c>
+      <c r="K636" s="14">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="637" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A637" s="13">
+        <f t="shared" si="0"/>
+        <v>46118</v>
+      </c>
+      <c r="B637" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C637" s="14">
+        <v>7.12</v>
+      </c>
+      <c r="D637" s="14">
+        <v>7.47</v>
+      </c>
+      <c r="E637" s="14">
+        <v>7.53</v>
+      </c>
+      <c r="F637" s="15">
+        <v>7.2173804178348178</v>
+      </c>
+      <c r="G637" s="14">
+        <v>7.49</v>
+      </c>
+      <c r="H637" s="14">
+        <v>7.35</v>
+      </c>
+      <c r="I637" s="14">
+        <v>7.44</v>
+      </c>
+      <c r="J637" s="14">
+        <v>7.69</v>
+      </c>
+      <c r="K637" s="14">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="638" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A638" s="13">
+        <f t="shared" si="0"/>
+        <v>46119</v>
+      </c>
+      <c r="B638" s="14">
+        <v>6.75</v>
+      </c>
+      <c r="C638" s="14">
+        <v>7.12</v>
+      </c>
+      <c r="D638" s="14">
+        <v>7.47</v>
+      </c>
+      <c r="E638" s="14">
+        <v>7.53</v>
+      </c>
+      <c r="F638" s="15">
+        <v>7.2173804178348178</v>
+      </c>
+      <c r="G638" s="14">
+        <v>7.49</v>
+      </c>
+      <c r="H638" s="14">
+        <v>7.35</v>
+      </c>
+      <c r="I638" s="14">
+        <v>7.44</v>
+      </c>
+      <c r="J638" s="14">
+        <v>7.69</v>
+      </c>
+      <c r="K638" s="14">
+        <v>8.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
